--- a/Analysis Examples/Cardex-Variance-Item-Analysis.xlsx
+++ b/Analysis Examples/Cardex-Variance-Item-Analysis.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item Roll Forward" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RR Analysis" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RR Analysis" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item Roll Forward" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Item Roll Forward'!$A$4:$U$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Item Roll Forward'!$A$4:$U$4</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -78,7 +78,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -133,6 +133,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFE0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD966"/>
       </patternFill>
     </fill>
   </fills>
@@ -222,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -468,6 +473,101 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -833,6 +933,730 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B70"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" style="65" min="1" max="1"/>
+    <col width="52" bestFit="1" customWidth="1" style="65" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1" s="65">
+      <c r="A1" s="80" t="inlineStr">
+        <is>
+          <t>RR Analysis — Standard Cost (Method 07) Quantity &amp; Amount Variance</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1" s="65">
+      <c r="A2" s="81" t="n"/>
+      <c r="B2" s="81" t="n"/>
+    </row>
+    <row r="3" ht="16" customHeight="1" s="65">
+      <c r="A3" s="82" t="inlineStr">
+        <is>
+          <t>DOCUMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1" s="65">
+      <c r="A4" s="83" t="inlineStr">
+        <is>
+          <t>Item Number</t>
+        </is>
+      </c>
+      <c r="B4" s="53" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1" s="65">
+      <c r="A5" s="83" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="B5" s="53" t="inlineStr">
+        <is>
+          <t>(none — no lot assigned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1" s="65">
+      <c r="A6" s="83" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="B6" s="53" t="inlineStr">
+        <is>
+          <t>IDM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1" s="65">
+      <c r="A7" s="83" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="B7" s="53" t="inlineStr">
+        <is>
+          <t>MLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1" s="65">
+      <c r="A8" s="83" t="inlineStr">
+        <is>
+          <t>GL Account</t>
+        </is>
+      </c>
+      <c r="B8" s="53" t="inlineStr">
+        <is>
+          <t>1000000.141000.CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1" s="65">
+      <c r="A9" s="83" t="inlineStr">
+        <is>
+          <t>GL Class</t>
+        </is>
+      </c>
+      <c r="B9" s="53" t="inlineStr">
+        <is>
+          <t>COLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1" s="65">
+      <c r="A10" s="83" t="inlineStr">
+        <is>
+          <t>UOM</t>
+        </is>
+      </c>
+      <c r="B10" s="53" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1" s="65">
+      <c r="A11" s="83" t="inlineStr">
+        <is>
+          <t>Analysis Date</t>
+        </is>
+      </c>
+      <c r="B11" s="53" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1" s="65">
+      <c r="A12" s="84" t="inlineStr">
+        <is>
+          <t>QtyVar</t>
+        </is>
+      </c>
+      <c r="B12" s="84" t="inlineStr">
+        <is>
+          <t>+10.35 LB  (F4111 ledger exceeds F41021 on-hand by 10.35 LB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1" s="65">
+      <c r="A13" s="84" t="inlineStr">
+        <is>
+          <t>AmtVar</t>
+        </is>
+      </c>
+      <c r="B13" s="84" t="inlineStr">
+        <is>
+          <t>+$59.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1" s="65">
+      <c r="A14" s="81" t="n"/>
+      <c r="B14" s="81" t="n"/>
+    </row>
+    <row r="15" ht="42" customHeight="1" s="65">
+      <c r="A15" s="82" t="inlineStr">
+        <is>
+          <t>COST METHOD  (dt field, ukid = 999999999999 — Curr bal row)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1" s="65">
+      <c r="A16" s="104" t="inlineStr">
+        <is>
+          <t>Cost Method Code</t>
+        </is>
+      </c>
+      <c r="B16" s="104" t="inlineStr">
+        <is>
+          <t>07 — Standard Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1" s="65">
+      <c r="A17" s="83" t="inlineStr">
+        <is>
+          <t>Standard cost</t>
+        </is>
+      </c>
+      <c r="B17" s="53" t="inlineStr">
+        <is>
+          <t>$5.72/LB (frozen in F4105, method 07) — consistent across all 21 transactions</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="98" customHeight="1" s="65">
+      <c r="A18" s="83" t="inlineStr">
+        <is>
+          <t>Implications</t>
+        </is>
+      </c>
+      <c r="B18" s="53" t="inlineStr">
+        <is>
+          <t>Costs are frozen from F30026 cost components. Key risks: (1) component/ledger mismatch — run R30543 or RR Integrity Report 6 to confirm F4105 method 07 equals sum of F30026 components; (2) WIP Revaluation — if standard cost was updated after open work orders were created, R30837 must be run from R30835 to revalue WIP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="84" customHeight="1" s="65">
+      <c r="A19" s="83" t="inlineStr">
+        <is>
+          <t>Cost integrity check</t>
+        </is>
+      </c>
+      <c r="B19" s="53" t="inlineStr">
+        <is>
+          <t>Single standard cost of $5.72/LB observed throughout all transactions. No cost drift detected. F4111 value (runamt $59.21) = runqty (10.35) × std cost ($5.72) = $59.202 — consistent with standard cost behaviour. Component/ledger mismatch is not the primary cause of this variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1" s="65">
+      <c r="A20" s="81" t="n"/>
+      <c r="B20" s="81" t="n"/>
+    </row>
+    <row r="21" ht="28" customHeight="1" s="65">
+      <c r="A21" s="82" t="inlineStr">
+        <is>
+          <t>COST LEVEL  (dt field, ukid = 0 — Beg bal row)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1" s="65">
+      <c r="A22" s="104" t="inlineStr">
+        <is>
+          <t>Cost Level Code</t>
+        </is>
+      </c>
+      <c r="B22" s="104" t="inlineStr">
+        <is>
+          <t>2 — Item/Branch level</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="56" customHeight="1" s="65">
+      <c r="A23" s="83" t="inlineStr">
+        <is>
+          <t>Reconciliation scope</t>
+        </is>
+      </c>
+      <c r="B23" s="53" t="inlineStr">
+        <is>
+          <t>F4111 summary and F41021 comparison performed at item/branch level, inclusive of all locations and lots. Location MLD is the only location present — no cross-location aggregation issues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1" s="65">
+      <c r="A24" s="81" t="n"/>
+      <c r="B24" s="81" t="n"/>
+    </row>
+    <row r="25" ht="28" customHeight="1" s="65">
+      <c r="A25" s="82" t="inlineStr">
+        <is>
+          <t>BEGINNING BALANCE  (ukid = 0 — Beg bal row)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1" s="65">
+      <c r="A26" s="83" t="inlineStr">
+        <is>
+          <t>Beg bal date</t>
+        </is>
+      </c>
+      <c r="B26" s="53" t="inlineStr">
+        <is>
+          <t>2015-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1" s="65">
+      <c r="A27" s="85" t="inlineStr">
+        <is>
+          <t>Beg bal qty</t>
+        </is>
+      </c>
+      <c r="B27" s="58" t="inlineStr">
+        <is>
+          <t>0.00 LB — zero opening balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1" s="65">
+      <c r="A28" s="83" t="inlineStr">
+        <is>
+          <t>Beg bal amount</t>
+        </is>
+      </c>
+      <c r="B28" s="53" t="inlineStr">
+        <is>
+          <t>$0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="84" customHeight="1" s="65">
+      <c r="A29" s="83" t="inlineStr">
+        <is>
+          <t>Beg bal integrity</t>
+        </is>
+      </c>
+      <c r="B29" s="53" t="inlineStr">
+        <is>
+          <t>PASS — Beg bal (0.00 LB) + net transactions (+10.35 LB) = Curr bal runqty (10.35 LB). F4111 ledger is internally consistent. The entire on-hand balance was built from transactions after RR go-live; the beginning balance itself is not the source of the variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1" s="65">
+      <c r="A30" s="81" t="n"/>
+      <c r="B30" s="81" t="n"/>
+    </row>
+    <row r="31" ht="28" customHeight="1" s="65">
+      <c r="A31" s="82" t="inlineStr">
+        <is>
+          <t>TRANSACTION SUMMARY (2015-02-12 to 2016-08-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1" s="65">
+      <c r="A32" s="86" t="inlineStr">
+        <is>
+          <t>IT (transfers)</t>
+        </is>
+      </c>
+      <c r="B32" s="60" t="inlineStr">
+        <is>
+          <t>15 transactions  |  Net qty: +4.900 LB  |  Net val: +$28.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1" s="65">
+      <c r="A33" s="84" t="inlineStr">
+        <is>
+          <t>IA (adjustments)</t>
+        </is>
+      </c>
+      <c r="B33" s="87" t="inlineStr">
+        <is>
+          <t>4 transactions   |  Net qty: +9.970 LB  |  Net val: +$57.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1" s="65">
+      <c r="A34" s="105" t="inlineStr">
+        <is>
+          <t>IM (WO issues)</t>
+        </is>
+      </c>
+      <c r="B34" s="106" t="inlineStr">
+        <is>
+          <t>2 transactions   |  Net qty: –4.520 LB  |  Net val: –$25.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1" s="65">
+      <c r="A35" s="83" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B35" s="53" t="inlineStr">
+        <is>
+          <t>Net qty: +10.350 LB  |  Net val: +$59.21  ✓  ties to Curr bal runqty and runamt</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1" s="65">
+      <c r="A36" s="81" t="n"/>
+      <c r="B36" s="81" t="n"/>
+    </row>
+    <row r="37" ht="16" customHeight="1" s="65">
+      <c r="A37" s="82" t="inlineStr">
+        <is>
+          <t>AMTVAR DECOMPOSITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1" s="65">
+      <c r="A38" s="84" t="inlineStr">
+        <is>
+          <t>QtyVar × std cost</t>
+        </is>
+      </c>
+      <c r="B38" s="87" t="inlineStr">
+        <is>
+          <t>+10.35 LB × $5.72 = $59.202  (Component A — resolved by correcting the quantity gap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1" s="65">
+      <c r="A39" s="83" t="inlineStr">
+        <is>
+          <t>Residual dollar-only</t>
+        </is>
+      </c>
+      <c r="B39" s="53" t="inlineStr">
+        <is>
+          <t>$59.15 – $59.202 = –$0.052  (Component B — immaterial rounding, no separate IA required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1" s="65">
+      <c r="A40" s="81" t="n"/>
+      <c r="B40" s="81" t="n"/>
+    </row>
+    <row r="41" ht="16" customHeight="1" s="65">
+      <c r="A41" s="82" t="inlineStr">
+        <is>
+          <t>ROOT CAUSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="56" customHeight="1" s="65">
+      <c r="A42" s="83" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B42" s="53" t="inlineStr">
+        <is>
+          <t>Section 4h — F41021 vs F4111 Integrity Gap (Quantity Variance). QtyVar = +10.35 LB; F4111 ledger is internally consistent; standard cost is stable throughout — WAC escalation is not a factor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="56" customHeight="1" s="65">
+      <c r="A43" s="84" t="inlineStr">
+        <is>
+          <t>Key finding</t>
+        </is>
+      </c>
+      <c r="B43" s="84" t="inlineStr">
+        <is>
+          <t>Curr bal runqty (10.35 LB) = QtyVar (10.35 LB). This means F41021 on-hand = 0 LB while F4111 records 10.35 LB. The entire current ledger balance is the variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="112" customHeight="1" s="65">
+      <c r="A44" s="84" t="inlineStr">
+        <is>
+          <t>Primary suspect — IA doc 167759</t>
+        </is>
+      </c>
+      <c r="B44" s="87" t="inlineStr">
+        <is>
+          <t>A single positive IA transaction (doc 167759, 'MAT. SOBR.', 2016-06-10) added +15.62 LB to F4111. The three prior negative IAs (Oct 2015) totalling –5.65 LB brought the balance to zero, after which this large positive IA is the sole source of the current 10.35 LB ledger balance. If this IA posted to F4111 but failed to update F41021, it fully explains the variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="84" customHeight="1" s="65">
+      <c r="A45" s="83" t="inlineStr">
+        <is>
+          <t>Post-IA IT activity</t>
+        </is>
+      </c>
+      <c r="B45" s="53" t="inlineStr">
+        <is>
+          <t>After the Jun 2016 IA, five IT transfers moved inventory in and out, netting –5.27 LB (15.62 – 5.27 = 10.35 LB current balance). If F41021 was zero throughout, these IT transactions also failed to update F41021, which is consistent with F41021 being stale since the missed IA posting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1" s="65">
+      <c r="A46" s="81" t="n"/>
+      <c r="B46" s="81" t="n"/>
+    </row>
+    <row r="47" ht="28" customHeight="1" s="65">
+      <c r="A47" s="82" t="inlineStr">
+        <is>
+          <t>EVIDENCE — SOURCE ROWS (Sheet: Item Roll Forward)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="28" customHeight="1" s="65">
+      <c r="A48" s="83" t="inlineStr">
+        <is>
+          <t>Curr bal row</t>
+        </is>
+      </c>
+      <c r="B48" s="53" t="inlineStr">
+        <is>
+          <t>Excel row 3 — runqty=10.35, runamt=$59.21, qtyvar=10.35, amtvar=$59.15  (AMBER)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28" customHeight="1" s="65">
+      <c r="A49" s="83" t="inlineStr">
+        <is>
+          <t>IA doc 167759</t>
+        </is>
+      </c>
+      <c r="B49" s="53" t="inlineStr">
+        <is>
+          <t>Excel row 5 — +15.62 LB IA 'MAT. SOBR.' 2016-06-10  (RED — root cause)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="28" customHeight="1" s="65">
+      <c r="A50" s="83" t="inlineStr">
+        <is>
+          <t>Negative IA rows</t>
+        </is>
+      </c>
+      <c r="B50" s="53" t="inlineStr">
+        <is>
+          <t>Excel rows 9–11 — three IAs Oct 2015 totalling –5.65 LB  (ORANGE — related)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1" s="65">
+      <c r="A51" s="83" t="inlineStr">
+        <is>
+          <t>Beg bal row</t>
+        </is>
+      </c>
+      <c r="B51" s="53" t="inlineStr">
+        <is>
+          <t>Excel row 23 — runqty=0.00, runamt=$0.00  (AMBER)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="16" customHeight="1" s="65">
+      <c r="A52" s="81" t="n"/>
+      <c r="B52" s="81" t="n"/>
+    </row>
+    <row r="53" ht="16" customHeight="1" s="65">
+      <c r="A53" s="82" t="inlineStr">
+        <is>
+          <t>CORRECTIVE ACTION — JDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="42" customHeight="1" s="65">
+      <c r="A54" s="83" t="inlineStr">
+        <is>
+          <t>Step 1 — Validate qty</t>
+        </is>
+      </c>
+      <c r="B54" s="53" t="inlineStr">
+        <is>
+          <t>Confirm F41021 on-hand qty = 0 LB for Item 555 / Branch IDM / Location MLD. If F41021 shows a non-zero value, re-scope the investigation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="56" customHeight="1" s="65">
+      <c r="A55" s="83" t="inlineStr">
+        <is>
+          <t>Step 2 — Check for unposted IA</t>
+        </is>
+      </c>
+      <c r="B55" s="53" t="inlineStr">
+        <is>
+          <t>Query F4111 for Item 555 / Branch IDM. Filter IA rows for ILIPCD ≠ 'P'. Focus on doc 167759 (2016-06-10, +15.62 LB). Also check GL Batches variance in RapidReconciler for outstanding unposted IA batches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="42" customHeight="1" s="65">
+      <c r="A56" s="83" t="inlineStr">
+        <is>
+          <t>Step 3a — If unposted batch found</t>
+        </is>
+      </c>
+      <c r="B56" s="53" t="inlineStr">
+        <is>
+          <t>Post the batch in JD Edwards. Recheck F41021 qty after posting. If F41021 updates to 10.35 LB, the variance is resolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="56" customHeight="1" s="65">
+      <c r="A57" s="83" t="inlineStr">
+        <is>
+          <t>Step 3b — If all batches posted</t>
+        </is>
+      </c>
+      <c r="B57" s="53" t="inlineStr">
+        <is>
+          <t>F41021 did not update when the IA processed. Request an F41021 SQL correction from IT for +10.35 LB. DBA support required. Confirm F4111 is the accurate record before proceeding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="70" customHeight="1" s="65">
+      <c r="A58" s="83" t="inlineStr">
+        <is>
+          <t>Step 4 — Standard cost check</t>
+        </is>
+      </c>
+      <c r="B58" s="53" t="inlineStr">
+        <is>
+          <t>Run R30543 or RR Integrity Report 6 to confirm F4105 method 07 ($5.72/LB) equals the sum of F30026 cost components. Consistent standard cost observed here makes a component/ledger mismatch unlikely, but this should be confirmed before closing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="28" customHeight="1" s="65">
+      <c r="A59" s="83" t="inlineStr">
+        <is>
+          <t>Step 5 — Dollar residual</t>
+        </is>
+      </c>
+      <c r="B59" s="53" t="inlineStr">
+        <is>
+          <t>Component B residual = –$0.052. Immaterial — no separate dollars-only IA required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="56" customHeight="1" s="65">
+      <c r="A60" s="83" t="inlineStr">
+        <is>
+          <t>Step 6 — Re-Roll in RapidReconciler</t>
+        </is>
+      </c>
+      <c r="B60" s="53" t="inlineStr">
+        <is>
+          <t>After JDE correction, open Re-Roll Item dialog for Item 555. Select Re-Roll Item. Verify details. Click Re-Roll. Confirm QtyVar = 0 and AmtVar = 0 after next nightly refresh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1" s="65">
+      <c r="A61" s="81" t="n"/>
+      <c r="B61" s="81" t="n"/>
+    </row>
+    <row r="62" ht="16" customHeight="1" s="65">
+      <c r="A62" s="82" t="inlineStr">
+        <is>
+          <t>PREVENTIVE ACTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="56" customHeight="1" s="65">
+      <c r="A63" s="83" t="inlineStr">
+        <is>
+          <t>1 — IA batch posting controls</t>
+        </is>
+      </c>
+      <c r="B63" s="53" t="inlineStr">
+        <is>
+          <t>Confirm all IA batches for Branch IDM auto-approve and auto-post. A single large positive IA (+15.62 LB) that failed to update F41021 is the likely origin of this variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="42" customHeight="1" s="65">
+      <c r="A64" s="83" t="inlineStr">
+        <is>
+          <t>2 — R30543 periodic review</t>
+        </is>
+      </c>
+      <c r="B64" s="53" t="inlineStr">
+        <is>
+          <t>Run R30543 (or use RR Integrity Report 6) before each period-end close to proactively identify standard cost component/ledger mismatches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="56" customHeight="1" s="65">
+      <c r="A65" s="83" t="inlineStr">
+        <is>
+          <t>3 — WIP Revaluation monitoring</t>
+        </is>
+      </c>
+      <c r="B65" s="53" t="inlineStr">
+        <is>
+          <t>If the $5.72/LB standard cost is updated in future, ensure R30837 is invoked from R30835 to revalue any open work orders. Failure to do so will leave WIP at the old standard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1" s="65">
+      <c r="A66" s="81" t="n"/>
+      <c r="B66" s="81" t="n"/>
+    </row>
+    <row r="67" ht="28" customHeight="1" s="65">
+      <c r="A67" s="82" t="inlineStr">
+        <is>
+          <t>OPEN ITEMS REQUIRING JDE INVESTIGATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="28" customHeight="1" s="65">
+      <c r="A68" s="83" t="inlineStr">
+        <is>
+          <t>?  F41021 current QOH</t>
+        </is>
+      </c>
+      <c r="B68" s="53" t="inlineStr">
+        <is>
+          <t>Confirm F41021 on-hand = 0 LB before posting any correction — cannot verify from Excel alone</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="28" customHeight="1" s="65">
+      <c r="A69" s="83" t="inlineStr">
+        <is>
+          <t>?  IA doc 167759 posting status</t>
+        </is>
+      </c>
+      <c r="B69" s="53" t="inlineStr">
+        <is>
+          <t>Query ILIPCD on this F4111 row — determine whether it posted correctly or failed to update F41021</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="28" customHeight="1" s="65">
+      <c r="A70" s="83" t="inlineStr">
+        <is>
+          <t>?  R30543 / Integrity Report 6</t>
+        </is>
+      </c>
+      <c r="B70" s="53" t="inlineStr">
+        <is>
+          <t>Confirm no component/ledger mismatch exists for Item 555 at current standard cost $5.72/LB</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A53:B53"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:U34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -972,330 +1796,330 @@
       </c>
     </row>
     <row r="3" ht="15.95" customHeight="1" s="65">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="107" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="107" t="inlineStr">
         <is>
           <t>1000000.141000.CC</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="108" t="n">
         <v>999999999999</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="107" t="inlineStr">
         <is>
           <t>IDM</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="107" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="107" t="inlineStr">
         <is>
           <t>MLD</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G3" s="107" t="n"/>
+      <c r="H3" s="107" t="inlineStr">
         <is>
           <t>COLC</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="52" t="inlineStr">
         <is>
           <t>2016-08-08</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="52" t="inlineStr">
         <is>
           <t>2016-08-27</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="107" t="inlineStr">
         <is>
           <t>Curr bal</t>
         </is>
       </c>
-      <c r="L3" s="5" t="n">
+      <c r="L3" s="109" t="n">
         <v>10.35</v>
       </c>
-      <c r="M3" s="6" t="n">
+      <c r="M3" s="110" t="n">
         <v>59.21</v>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="107" t="inlineStr">
         <is>
           <t>07</t>
         </is>
       </c>
-      <c r="O3" s="3" t="n"/>
-      <c r="P3" s="7" t="n">
+      <c r="O3" s="108" t="n"/>
+      <c r="P3" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" s="107" t="inlineStr">
         <is>
           <t>LB</t>
         </is>
       </c>
-      <c r="R3" s="8" t="n">
+      <c r="R3" s="112" t="n">
         <v>5.72</v>
       </c>
-      <c r="S3" s="6" t="n">
+      <c r="S3" s="110" t="n">
         <v>0</v>
       </c>
-      <c r="T3" s="9" t="n">
+      <c r="T3" s="113" t="n">
         <v>10.35</v>
       </c>
-      <c r="U3" s="10" t="n">
+      <c r="U3" s="114" t="n">
         <v>59.15</v>
       </c>
     </row>
     <row r="4" ht="15.95" customHeight="1" s="65">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="115" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="115" t="inlineStr">
         <is>
           <t>1000000.141000.CC</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n">
+      <c r="C4" s="116" t="n">
         <v>39725584</v>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="115" t="inlineStr">
         <is>
           <t>IDM</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="115" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="115" t="inlineStr">
         <is>
           <t>MLD</t>
         </is>
       </c>
-      <c r="G4" s="11" t="n"/>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="G4" s="115" t="n"/>
+      <c r="H4" s="115" t="inlineStr">
         <is>
           <t>COLC</t>
         </is>
       </c>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="I4" s="68" t="inlineStr">
         <is>
           <t>2016-08-08</t>
         </is>
       </c>
-      <c r="J4" s="13" t="inlineStr">
+      <c r="J4" s="68" t="inlineStr">
         <is>
           <t>2016-08-27</t>
         </is>
       </c>
-      <c r="K4" s="11" t="inlineStr">
+      <c r="K4" s="115" t="inlineStr">
         <is>
           <t>TRAS.MAT.</t>
         </is>
       </c>
-      <c r="L4" s="14" t="n">
+      <c r="L4" s="117" t="n">
         <v>10.35</v>
       </c>
-      <c r="M4" s="15" t="n">
+      <c r="M4" s="118" t="n">
         <v>59.21</v>
       </c>
-      <c r="N4" s="11" t="inlineStr">
+      <c r="N4" s="115" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="O4" s="12" t="n">
+      <c r="O4" s="116" t="n">
         <v>2402120</v>
       </c>
-      <c r="P4" s="16" t="n">
+      <c r="P4" s="119" t="n">
         <v>-1</v>
       </c>
-      <c r="Q4" s="11" t="inlineStr">
+      <c r="Q4" s="115" t="inlineStr">
         <is>
           <t>LB</t>
         </is>
       </c>
-      <c r="R4" s="17" t="n">
+      <c r="R4" s="120" t="n">
         <v>5.72</v>
       </c>
-      <c r="S4" s="15" t="n">
+      <c r="S4" s="118" t="n">
         <v>-5.72</v>
       </c>
-      <c r="T4" s="16" t="n"/>
-      <c r="U4" s="15" t="n"/>
+      <c r="T4" s="119" t="n"/>
+      <c r="U4" s="118" t="n"/>
     </row>
     <row r="5" ht="15.95" customHeight="1" s="65">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="115" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="115" t="inlineStr">
         <is>
           <t>1000000.141000.CC</t>
         </is>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="116" t="n">
         <v>39564870</v>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="115" t="inlineStr">
         <is>
           <t>IDM</t>
         </is>
       </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="E5" s="115" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F5" s="115" t="inlineStr">
         <is>
           <t>MLD</t>
         </is>
       </c>
-      <c r="G5" s="18" t="n"/>
-      <c r="H5" s="18" t="inlineStr">
+      <c r="G5" s="115" t="n"/>
+      <c r="H5" s="115" t="inlineStr">
         <is>
           <t>COLC</t>
         </is>
       </c>
-      <c r="I5" s="20" t="inlineStr">
+      <c r="I5" s="68" t="inlineStr">
         <is>
           <t>2016-07-22</t>
         </is>
       </c>
-      <c r="J5" s="20" t="inlineStr">
+      <c r="J5" s="68" t="inlineStr">
         <is>
           <t>2016-07-30</t>
         </is>
       </c>
-      <c r="K5" s="18" t="inlineStr">
+      <c r="K5" s="115" t="inlineStr">
         <is>
           <t>TRAS. MAT.</t>
         </is>
       </c>
-      <c r="L5" s="21" t="n">
+      <c r="L5" s="117" t="n">
         <v>11.35</v>
       </c>
-      <c r="M5" s="22" t="n">
+      <c r="M5" s="118" t="n">
         <v>64.93000000000001</v>
       </c>
-      <c r="N5" s="18" t="inlineStr">
+      <c r="N5" s="115" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="O5" s="19" t="n">
+      <c r="O5" s="116" t="n">
         <v>2394517</v>
       </c>
-      <c r="P5" s="23" t="n">
+      <c r="P5" s="119" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" s="18" t="inlineStr">
+      <c r="Q5" s="115" t="inlineStr">
         <is>
           <t>LB</t>
         </is>
       </c>
-      <c r="R5" s="24" t="n">
+      <c r="R5" s="120" t="n">
         <v>5.72</v>
       </c>
-      <c r="S5" s="22" t="n">
+      <c r="S5" s="118" t="n">
         <v>5.72</v>
       </c>
-      <c r="T5" s="23" t="n"/>
-      <c r="U5" s="22" t="n"/>
+      <c r="T5" s="119" t="n"/>
+      <c r="U5" s="118" t="n"/>
     </row>
     <row r="6" ht="15.95" customHeight="1" s="65">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="115" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="115" t="inlineStr">
         <is>
           <t>1000000.141000.CC</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="116" t="n">
         <v>39314173</v>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="115" t="inlineStr">
         <is>
           <t>IDM</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="115" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="115" t="inlineStr">
         <is>
           <t>MLD</t>
         </is>
       </c>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="G6" s="115" t="n"/>
+      <c r="H6" s="115" t="inlineStr">
         <is>
           <t>COLC</t>
         </is>
       </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="I6" s="68" t="inlineStr">
         <is>
           <t>2016-06-27</t>
         </is>
       </c>
-      <c r="J6" s="13" t="inlineStr">
+      <c r="J6" s="68" t="inlineStr">
         <is>
           <t>2016-07-02</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="K6" s="115" t="inlineStr">
         <is>
           <t>MAT. TRAS.</t>
         </is>
       </c>
-      <c r="L6" s="14" t="n">
+      <c r="L6" s="117" t="n">
         <v>10.35</v>
       </c>
-      <c r="M6" s="15" t="n">
+      <c r="M6" s="118" t="n">
         <v>59.21</v>
       </c>
-      <c r="N6" s="11" t="inlineStr">
+      <c r="N6" s="115" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="O6" s="12" t="n">
+      <c r="O6" s="116" t="n">
         <v>2380912</v>
       </c>
-      <c r="P6" s="16" t="n">
+      <c r="P6" s="119" t="n">
         <v>-5.27</v>
       </c>
-      <c r="Q6" s="11" t="inlineStr">
+      <c r="Q6" s="115" t="inlineStr">
         <is>
           <t>LB</t>
         </is>
       </c>
-      <c r="R6" s="17" t="n">
+      <c r="R6" s="120" t="n">
         <v>5.72</v>
       </c>
-      <c r="S6" s="15" t="n">
+      <c r="S6" s="118" t="n">
         <v>-30.14</v>
       </c>
-      <c r="T6" s="16" t="n"/>
-      <c r="U6" s="15" t="n"/>
+      <c r="T6" s="119" t="n"/>
+      <c r="U6" s="118" t="n"/>
     </row>
     <row r="7" ht="15.95" customHeight="1" s="65">
       <c r="A7" s="70" t="inlineStr">
@@ -1379,1463 +2203,1461 @@
       <c r="U7" s="74" t="n"/>
     </row>
     <row r="8" ht="15.95" customHeight="1" s="65">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="115" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="115" t="inlineStr">
         <is>
           <t>1000000.141000.CC</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="116" t="n">
         <v>38354197</v>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="115" t="inlineStr">
         <is>
           <t>IDM</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="115" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="115" t="inlineStr">
         <is>
           <t>MLD</t>
         </is>
       </c>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="G8" s="115" t="n"/>
+      <c r="H8" s="115" t="inlineStr">
         <is>
           <t>COLC</t>
         </is>
       </c>
-      <c r="I8" s="13" t="inlineStr">
+      <c r="I8" s="68" t="inlineStr">
         <is>
           <t>2016-04-01</t>
         </is>
       </c>
-      <c r="J8" s="13" t="inlineStr">
+      <c r="J8" s="68" t="inlineStr">
         <is>
           <t>2016-04-02</t>
         </is>
       </c>
-      <c r="K8" s="11" t="inlineStr">
+      <c r="K8" s="115" t="inlineStr">
         <is>
           <t>TRAS.MAT.</t>
         </is>
       </c>
-      <c r="L8" s="14" t="n">
+      <c r="L8" s="117" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="15" t="n">
+      <c r="M8" s="118" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="11" t="inlineStr">
+      <c r="N8" s="115" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="O8" s="12" t="n">
+      <c r="O8" s="116" t="n">
         <v>2329013</v>
       </c>
-      <c r="P8" s="16" t="n">
+      <c r="P8" s="119" t="n">
         <v>-7.68</v>
       </c>
-      <c r="Q8" s="11" t="inlineStr">
+      <c r="Q8" s="115" t="inlineStr">
         <is>
           <t>LB</t>
         </is>
       </c>
-      <c r="R8" s="17" t="n">
+      <c r="R8" s="120" t="n">
         <v>5.72</v>
       </c>
-      <c r="S8" s="15" t="n">
+      <c r="S8" s="118" t="n">
         <v>-43.93</v>
       </c>
-      <c r="T8" s="16" t="n"/>
-      <c r="U8" s="15" t="n"/>
+      <c r="T8" s="119" t="n"/>
+      <c r="U8" s="118" t="n"/>
     </row>
     <row r="9" ht="15.95" customHeight="1" s="65">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="A9" s="89" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" s="89" t="inlineStr">
         <is>
           <t>1000000.141000.CC</t>
         </is>
       </c>
-      <c r="C9" s="33" t="n">
+      <c r="C9" s="90" t="n">
         <v>38290332</v>
       </c>
-      <c r="D9" s="32" t="inlineStr">
+      <c r="D9" s="89" t="inlineStr">
         <is>
           <t>IDM</t>
         </is>
       </c>
-      <c r="E9" s="32" t="inlineStr">
+      <c r="E9" s="89" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="F9" s="32" t="inlineStr">
+      <c r="F9" s="89" t="inlineStr">
         <is>
           <t>MLD</t>
         </is>
       </c>
-      <c r="G9" s="32" t="n"/>
-      <c r="H9" s="32" t="inlineStr">
+      <c r="G9" s="89" t="n"/>
+      <c r="H9" s="89" t="inlineStr">
         <is>
           <t>COLC</t>
         </is>
       </c>
-      <c r="I9" s="34" t="inlineStr">
+      <c r="I9" s="91" t="inlineStr">
         <is>
           <t>2016-03-28</t>
         </is>
       </c>
-      <c r="J9" s="34" t="inlineStr">
+      <c r="J9" s="91" t="inlineStr">
         <is>
           <t>2016-04-02</t>
         </is>
       </c>
-      <c r="K9" s="32" t="inlineStr">
+      <c r="K9" s="89" t="inlineStr">
         <is>
           <t>Material C</t>
         </is>
       </c>
-      <c r="L9" s="35" t="n">
+      <c r="L9" s="92" t="n">
         <v>7.68</v>
       </c>
-      <c r="M9" s="36" t="n">
+      <c r="M9" s="93" t="n">
         <v>43.93</v>
       </c>
-      <c r="N9" s="32" t="inlineStr">
+      <c r="N9" s="89" t="inlineStr">
         <is>
           <t>IM</t>
         </is>
       </c>
-      <c r="O9" s="33" t="n">
+      <c r="O9" s="90" t="n">
         <v>1270536</v>
       </c>
-      <c r="P9" s="37" t="n">
+      <c r="P9" s="94" t="n">
         <v>-4.32</v>
       </c>
-      <c r="Q9" s="32" t="inlineStr">
+      <c r="Q9" s="89" t="inlineStr">
         <is>
           <t>LB</t>
         </is>
       </c>
-      <c r="R9" s="38" t="n">
+      <c r="R9" s="95" t="n">
         <v>5.72</v>
       </c>
-      <c r="S9" s="36" t="n">
+      <c r="S9" s="93" t="n">
         <v>-24.71</v>
       </c>
-      <c r="T9" s="37" t="n"/>
-      <c r="U9" s="36" t="n"/>
+      <c r="T9" s="94" t="n"/>
+      <c r="U9" s="93" t="n"/>
     </row>
     <row r="10" ht="15.95" customHeight="1" s="65">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="115" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="115" t="inlineStr">
         <is>
           <t>1000000.141000.CC</t>
         </is>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="C10" s="116" t="n">
         <v>38124670</v>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="115" t="inlineStr">
         <is>
           <t>IDM</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" s="115" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="115" t="inlineStr">
         <is>
           <t>MLD</t>
         </is>
       </c>
-      <c r="G10" s="18" t="n"/>
-      <c r="H10" s="18" t="inlineStr">
+      <c r="G10" s="115" t="n"/>
+      <c r="H10" s="115" t="inlineStr">
         <is>
           <t>COLC</t>
         </is>
       </c>
-      <c r="I10" s="20" t="inlineStr">
+      <c r="I10" s="68" t="inlineStr">
         <is>
           <t>2016-03-10</t>
         </is>
       </c>
-      <c r="J10" s="20" t="inlineStr">
+      <c r="J10" s="68" t="inlineStr">
         <is>
           <t>2016-04-02</t>
         </is>
       </c>
-      <c r="K10" s="18" t="inlineStr">
+      <c r="K10" s="115" t="inlineStr">
         <is>
           <t>WHS A MLD</t>
         </is>
       </c>
-      <c r="L10" s="21" t="n">
+      <c r="L10" s="117" t="n">
         <v>12</v>
       </c>
-      <c r="M10" s="22" t="n">
+      <c r="M10" s="118" t="n">
         <v>68.64</v>
       </c>
-      <c r="N10" s="18" t="inlineStr">
+      <c r="N10" s="115" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="O10" s="19" t="n">
+      <c r="O10" s="116" t="n">
         <v>2316880</v>
       </c>
-      <c r="P10" s="23" t="n">
+      <c r="P10" s="119" t="n">
         <v>12</v>
       </c>
-      <c r="Q10" s="18" t="inlineStr">
+      <c r="Q10" s="115" t="inlineStr">
         <is>
           <t>LB</t>
         </is>
       </c>
-      <c r="R10" s="24" t="n">
+      <c r="R10" s="120" t="n">
         <v>5.72</v>
       </c>
-      <c r="S10" s="22" t="n">
+      <c r="S10" s="118" t="n">
         <v>68.64</v>
       </c>
-      <c r="T10" s="23" t="n"/>
-      <c r="U10" s="22" t="n"/>
+      <c r="T10" s="119" t="n"/>
+      <c r="U10" s="118" t="n"/>
     </row>
     <row r="11" ht="15.95" customHeight="1" s="65">
-      <c r="A11" s="39" t="inlineStr">
+      <c r="A11" s="115" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B11" s="39" t="inlineStr">
+      <c r="B11" s="115" t="inlineStr">
         <is>
           <t>1000000.141000.CC</t>
         </is>
       </c>
-      <c r="C11" s="40" t="n">
+      <c r="C11" s="116" t="n">
         <v>36601693</v>
       </c>
-      <c r="D11" s="39" t="inlineStr">
+      <c r="D11" s="115" t="inlineStr">
         <is>
           <t>IDM</t>
         </is>
       </c>
-      <c r="E11" s="39" t="inlineStr">
+      <c r="E11" s="115" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="F11" s="39" t="inlineStr">
+      <c r="F11" s="115" t="inlineStr">
         <is>
           <t>MLD</t>
         </is>
       </c>
-      <c r="G11" s="39" t="n"/>
-      <c r="H11" s="39" t="inlineStr">
+      <c r="G11" s="115" t="n"/>
+      <c r="H11" s="115" t="inlineStr">
         <is>
           <t>COLC</t>
         </is>
       </c>
-      <c r="I11" s="41" t="inlineStr">
+      <c r="I11" s="68" t="inlineStr">
         <is>
           <t>2015-10-10</t>
         </is>
       </c>
-      <c r="J11" s="41" t="inlineStr">
+      <c r="J11" s="68" t="inlineStr">
         <is>
           <t>2015-10-31</t>
         </is>
       </c>
-      <c r="K11" s="39" t="inlineStr">
+      <c r="K11" s="115" t="inlineStr">
         <is>
           <t>046.03.007</t>
         </is>
       </c>
-      <c r="L11" s="42" t="n">
+      <c r="L11" s="117" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="43" t="n">
+      <c r="M11" s="118" t="n">
         <v>0</v>
       </c>
-      <c r="N11" s="39" t="inlineStr">
+      <c r="N11" s="115" t="inlineStr">
         <is>
           <t>IA</t>
         </is>
       </c>
-      <c r="O11" s="40" t="n">
+      <c r="O11" s="116" t="n">
         <v>145500</v>
       </c>
-      <c r="P11" s="44" t="n">
+      <c r="P11" s="119" t="n">
         <v>-2</v>
       </c>
-      <c r="Q11" s="39" t="inlineStr">
+      <c r="Q11" s="115" t="inlineStr">
         <is>
           <t>LB</t>
         </is>
       </c>
-      <c r="R11" s="45" t="n">
+      <c r="R11" s="120" t="n">
         <v>5.72</v>
       </c>
-      <c r="S11" s="43" t="n">
+      <c r="S11" s="118" t="n">
         <v>-11.44</v>
       </c>
-      <c r="T11" s="44" t="n"/>
-      <c r="U11" s="43" t="n"/>
+      <c r="T11" s="119" t="n"/>
+      <c r="U11" s="118" t="n"/>
     </row>
     <row r="12" ht="15.95" customHeight="1" s="65">
-      <c r="A12" s="39" t="inlineStr">
+      <c r="A12" s="115" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B12" s="39" t="inlineStr">
+      <c r="B12" s="115" t="inlineStr">
         <is>
           <t>1000000.141000.CC</t>
         </is>
       </c>
-      <c r="C12" s="40" t="n">
+      <c r="C12" s="116" t="n">
         <v>36544809</v>
       </c>
-      <c r="D12" s="39" t="inlineStr">
+      <c r="D12" s="115" t="inlineStr">
         <is>
           <t>IDM</t>
         </is>
       </c>
-      <c r="E12" s="39" t="inlineStr">
+      <c r="E12" s="115" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="F12" s="39" t="inlineStr">
+      <c r="F12" s="115" t="inlineStr">
         <is>
           <t>MLD</t>
         </is>
       </c>
-      <c r="G12" s="39" t="n"/>
-      <c r="H12" s="39" t="inlineStr">
+      <c r="G12" s="115" t="n"/>
+      <c r="H12" s="115" t="inlineStr">
         <is>
           <t>COLC</t>
         </is>
       </c>
-      <c r="I12" s="41" t="inlineStr">
+      <c r="I12" s="68" t="inlineStr">
         <is>
           <t>2015-10-06</t>
         </is>
       </c>
-      <c r="J12" s="41" t="inlineStr">
+      <c r="J12" s="68" t="inlineStr">
         <is>
           <t>2015-10-31</t>
         </is>
       </c>
-      <c r="K12" s="39" t="inlineStr">
+      <c r="K12" s="115" t="inlineStr">
         <is>
           <t>046-03-007</t>
         </is>
       </c>
-      <c r="L12" s="42" t="n">
+      <c r="L12" s="117" t="n">
         <v>2</v>
       </c>
-      <c r="M12" s="43" t="n">
+      <c r="M12" s="118" t="n">
         <v>11.44</v>
       </c>
-      <c r="N12" s="39" t="inlineStr">
+      <c r="N12" s="115" t="inlineStr">
         <is>
           <t>IA</t>
         </is>
       </c>
-      <c r="O12" s="40" t="n">
+      <c r="O12" s="116" t="n">
         <v>144973</v>
       </c>
-      <c r="P12" s="44" t="n">
+      <c r="P12" s="119" t="n">
         <v>-1</v>
       </c>
-      <c r="Q12" s="39" t="inlineStr">
+      <c r="Q12" s="115" t="inlineStr">
         <is>
           <t>LB</t>
         </is>
       </c>
-      <c r="R12" s="45" t="n">
+      <c r="R12" s="120" t="n">
         <v>5.72</v>
       </c>
-      <c r="S12" s="43" t="n">
+      <c r="S12" s="118" t="n">
         <v>-5.72</v>
       </c>
-      <c r="T12" s="44" t="n"/>
-      <c r="U12" s="43" t="n"/>
+      <c r="T12" s="119" t="n"/>
+      <c r="U12" s="118" t="n"/>
     </row>
     <row r="13" ht="15.95" customHeight="1" s="65">
-      <c r="A13" s="39" t="inlineStr">
+      <c r="A13" s="115" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B13" s="39" t="inlineStr">
+      <c r="B13" s="115" t="inlineStr">
         <is>
           <t>1000000.141000.CC</t>
         </is>
       </c>
-      <c r="C13" s="40" t="n">
+      <c r="C13" s="116" t="n">
         <v>36449935</v>
       </c>
-      <c r="D13" s="39" t="inlineStr">
+      <c r="D13" s="115" t="inlineStr">
         <is>
           <t>IDM</t>
         </is>
       </c>
-      <c r="E13" s="39" t="inlineStr">
+      <c r="E13" s="115" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="F13" s="39" t="inlineStr">
+      <c r="F13" s="115" t="inlineStr">
         <is>
           <t>MLD</t>
         </is>
       </c>
-      <c r="G13" s="39" t="n"/>
-      <c r="H13" s="39" t="inlineStr">
+      <c r="G13" s="115" t="n"/>
+      <c r="H13" s="115" t="inlineStr">
         <is>
           <t>COLC</t>
         </is>
       </c>
-      <c r="I13" s="41" t="inlineStr">
+      <c r="I13" s="68" t="inlineStr">
         <is>
           <t>2015-09-26</t>
         </is>
       </c>
-      <c r="J13" s="41" t="inlineStr">
+      <c r="J13" s="68" t="inlineStr">
         <is>
           <t>2015-10-03</t>
         </is>
       </c>
-      <c r="K13" s="39" t="inlineStr">
+      <c r="K13" s="115" t="inlineStr">
         <is>
           <t>046.03.007</t>
         </is>
       </c>
-      <c r="L13" s="42" t="n">
+      <c r="L13" s="117" t="n">
         <v>3</v>
       </c>
-      <c r="M13" s="43" t="n">
+      <c r="M13" s="118" t="n">
         <v>17.16</v>
       </c>
-      <c r="N13" s="39" t="inlineStr">
+      <c r="N13" s="115" t="inlineStr">
         <is>
           <t>IA</t>
         </is>
       </c>
-      <c r="O13" s="40" t="n">
+      <c r="O13" s="116" t="n">
         <v>143948</v>
       </c>
-      <c r="P13" s="44" t="n">
+      <c r="P13" s="119" t="n">
         <v>-2.65</v>
       </c>
-      <c r="Q13" s="39" t="inlineStr">
+      <c r="Q13" s="115" t="inlineStr">
         <is>
           <t>LB</t>
         </is>
       </c>
-      <c r="R13" s="45" t="n">
+      <c r="R13" s="120" t="n">
         <v>5.72</v>
       </c>
-      <c r="S13" s="43" t="n">
+      <c r="S13" s="118" t="n">
         <v>-15.16</v>
       </c>
-      <c r="T13" s="44" t="n"/>
-      <c r="U13" s="43" t="n"/>
+      <c r="T13" s="119" t="n"/>
+      <c r="U13" s="118" t="n"/>
     </row>
     <row r="14" ht="15.95" customHeight="1" s="65">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="115" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="115" t="inlineStr">
         <is>
           <t>1000000.141000.CC</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="C14" s="116" t="n">
         <v>36420663</v>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="115" t="inlineStr">
         <is>
           <t>IDM</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="115" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="115" t="inlineStr">
         <is>
           <t>MLD</t>
         </is>
       </c>
-      <c r="G14" s="11" t="n"/>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="G14" s="115" t="n"/>
+      <c r="H14" s="115" t="inlineStr">
         <is>
           <t>COLC</t>
         </is>
       </c>
-      <c r="I14" s="13" t="inlineStr">
+      <c r="I14" s="68" t="inlineStr">
         <is>
           <t>2015-09-24</t>
         </is>
       </c>
-      <c r="J14" s="13" t="inlineStr">
+      <c r="J14" s="68" t="inlineStr">
         <is>
           <t>2015-10-03</t>
         </is>
       </c>
-      <c r="K14" s="11" t="inlineStr">
+      <c r="K14" s="115" t="inlineStr">
         <is>
           <t>TRAS. MAT.</t>
         </is>
       </c>
-      <c r="L14" s="14" t="n">
+      <c r="L14" s="117" t="n">
         <v>5.65</v>
       </c>
-      <c r="M14" s="15" t="n">
+      <c r="M14" s="118" t="n">
         <v>32.32</v>
       </c>
-      <c r="N14" s="11" t="inlineStr">
+      <c r="N14" s="115" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="O14" s="12" t="n">
+      <c r="O14" s="116" t="n">
         <v>2222583</v>
       </c>
-      <c r="P14" s="16" t="n">
+      <c r="P14" s="119" t="n">
         <v>-6.35</v>
       </c>
-      <c r="Q14" s="11" t="inlineStr">
+      <c r="Q14" s="115" t="inlineStr">
         <is>
           <t>LB</t>
         </is>
       </c>
-      <c r="R14" s="17" t="n">
+      <c r="R14" s="120" t="n">
         <v>5.72</v>
       </c>
-      <c r="S14" s="15" t="n">
+      <c r="S14" s="118" t="n">
         <v>-36.32</v>
       </c>
-      <c r="T14" s="16" t="n"/>
-      <c r="U14" s="15" t="n"/>
+      <c r="T14" s="119" t="n"/>
+      <c r="U14" s="118" t="n"/>
     </row>
     <row r="15" ht="15.95" customHeight="1" s="65">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="115" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="115" t="inlineStr">
         <is>
           <t>1000000.141000.CC</t>
         </is>
       </c>
-      <c r="C15" s="19" t="n">
+      <c r="C15" s="116" t="n">
         <v>36396849</v>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D15" s="115" t="inlineStr">
         <is>
           <t>IDM</t>
         </is>
       </c>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="E15" s="115" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="F15" s="115" t="inlineStr">
         <is>
           <t>MLD</t>
         </is>
       </c>
-      <c r="G15" s="18" t="n"/>
-      <c r="H15" s="18" t="inlineStr">
+      <c r="G15" s="115" t="n"/>
+      <c r="H15" s="115" t="inlineStr">
         <is>
           <t>COLC</t>
         </is>
       </c>
-      <c r="I15" s="20" t="inlineStr">
+      <c r="I15" s="68" t="inlineStr">
         <is>
           <t>2015-09-22</t>
         </is>
       </c>
-      <c r="J15" s="20" t="inlineStr">
+      <c r="J15" s="68" t="inlineStr">
         <is>
           <t>2015-10-03</t>
         </is>
       </c>
-      <c r="K15" s="18" t="inlineStr">
+      <c r="K15" s="115" t="inlineStr">
         <is>
           <t>TRAS. MAT.</t>
         </is>
       </c>
-      <c r="L15" s="21" t="n">
+      <c r="L15" s="117" t="n">
         <v>12</v>
       </c>
-      <c r="M15" s="22" t="n">
+      <c r="M15" s="118" t="n">
         <v>68.64</v>
       </c>
-      <c r="N15" s="18" t="inlineStr">
+      <c r="N15" s="115" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="O15" s="19" t="n">
+      <c r="O15" s="116" t="n">
         <v>2221550</v>
       </c>
-      <c r="P15" s="23" t="n">
+      <c r="P15" s="119" t="n">
         <v>12</v>
       </c>
-      <c r="Q15" s="18" t="inlineStr">
+      <c r="Q15" s="115" t="inlineStr">
         <is>
           <t>LB</t>
         </is>
       </c>
-      <c r="R15" s="24" t="n">
+      <c r="R15" s="120" t="n">
         <v>5.72</v>
       </c>
-      <c r="S15" s="22" t="n">
+      <c r="S15" s="118" t="n">
         <v>68.64</v>
       </c>
-      <c r="T15" s="23" t="n"/>
-      <c r="U15" s="22" t="n"/>
+      <c r="T15" s="119" t="n"/>
+      <c r="U15" s="118" t="n"/>
     </row>
     <row r="16" ht="15.95" customHeight="1" s="65">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="115" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="115" t="inlineStr">
         <is>
           <t>1000000.141000.CC</t>
         </is>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="C16" s="116" t="n">
         <v>34696266</v>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="115" t="inlineStr">
         <is>
           <t>IDM</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="115" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="115" t="inlineStr">
         <is>
           <t>MLD</t>
         </is>
       </c>
-      <c r="G16" s="11" t="n"/>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="G16" s="115" t="n"/>
+      <c r="H16" s="115" t="inlineStr">
         <is>
           <t>COLC</t>
         </is>
       </c>
-      <c r="I16" s="13" t="inlineStr">
+      <c r="I16" s="68" t="inlineStr">
         <is>
           <t>2015-04-09</t>
         </is>
       </c>
-      <c r="J16" s="13" t="inlineStr">
+      <c r="J16" s="68" t="inlineStr">
         <is>
           <t>2015-05-02</t>
         </is>
       </c>
-      <c r="K16" s="11" t="inlineStr">
+      <c r="K16" s="115" t="inlineStr">
         <is>
           <t>TRAS. MAT.</t>
         </is>
       </c>
-      <c r="L16" s="14" t="n">
+      <c r="L16" s="117" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="15" t="n">
+      <c r="M16" s="118" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="11" t="inlineStr">
+      <c r="N16" s="115" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="O16" s="12" t="n">
+      <c r="O16" s="116" t="n">
         <v>2123876</v>
       </c>
-      <c r="P16" s="16" t="n">
+      <c r="P16" s="119" t="n">
         <v>-60</v>
       </c>
-      <c r="Q16" s="11" t="inlineStr">
+      <c r="Q16" s="115" t="inlineStr">
         <is>
           <t>LB</t>
         </is>
       </c>
-      <c r="R16" s="17" t="n">
+      <c r="R16" s="120" t="n">
         <v>5.72</v>
       </c>
-      <c r="S16" s="15" t="n">
+      <c r="S16" s="118" t="n">
         <v>-343.2</v>
       </c>
-      <c r="T16" s="16" t="n"/>
-      <c r="U16" s="15" t="n"/>
+      <c r="T16" s="119" t="n"/>
+      <c r="U16" s="118" t="n"/>
     </row>
     <row r="17" ht="15.95" customHeight="1" s="65">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="115" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="115" t="inlineStr">
         <is>
           <t>1000000.141000.CC</t>
         </is>
       </c>
-      <c r="C17" s="19" t="n">
+      <c r="C17" s="116" t="n">
         <v>34659593</v>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D17" s="115" t="inlineStr">
         <is>
           <t>IDM</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E17" s="115" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="F17" s="18" t="inlineStr">
+      <c r="F17" s="115" t="inlineStr">
         <is>
           <t>MLD</t>
         </is>
       </c>
-      <c r="G17" s="18" t="n"/>
-      <c r="H17" s="18" t="inlineStr">
+      <c r="G17" s="115" t="n"/>
+      <c r="H17" s="115" t="inlineStr">
         <is>
           <t>COLC</t>
         </is>
       </c>
-      <c r="I17" s="20" t="inlineStr">
+      <c r="I17" s="68" t="inlineStr">
         <is>
           <t>2015-04-07</t>
         </is>
       </c>
-      <c r="J17" s="20" t="inlineStr">
+      <c r="J17" s="68" t="inlineStr">
         <is>
           <t>2015-05-02</t>
         </is>
       </c>
-      <c r="K17" s="18" t="inlineStr">
+      <c r="K17" s="115" t="inlineStr">
         <is>
           <t>TRAS. MAT.</t>
         </is>
       </c>
-      <c r="L17" s="21" t="n">
+      <c r="L17" s="117" t="n">
         <v>60</v>
       </c>
-      <c r="M17" s="22" t="n">
+      <c r="M17" s="118" t="n">
         <v>343.2</v>
       </c>
-      <c r="N17" s="18" t="inlineStr">
+      <c r="N17" s="115" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="O17" s="19" t="n">
+      <c r="O17" s="116" t="n">
         <v>2121595</v>
       </c>
-      <c r="P17" s="23" t="n">
+      <c r="P17" s="119" t="n">
         <v>60</v>
       </c>
-      <c r="Q17" s="18" t="inlineStr">
+      <c r="Q17" s="115" t="inlineStr">
         <is>
           <t>LB</t>
         </is>
       </c>
-      <c r="R17" s="24" t="n">
+      <c r="R17" s="120" t="n">
         <v>5.72</v>
       </c>
-      <c r="S17" s="22" t="n">
+      <c r="S17" s="118" t="n">
         <v>343.2</v>
       </c>
-      <c r="T17" s="23" t="n"/>
-      <c r="U17" s="22" t="n"/>
+      <c r="T17" s="119" t="n"/>
+      <c r="U17" s="118" t="n"/>
     </row>
     <row r="18" ht="15.95" customHeight="1" s="65">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="115" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="115" t="inlineStr">
         <is>
           <t>1000000.141000.CC</t>
         </is>
       </c>
-      <c r="C18" s="12" t="n">
+      <c r="C18" s="116" t="n">
         <v>34589935</v>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="115" t="inlineStr">
         <is>
           <t>IDM</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="115" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="115" t="inlineStr">
         <is>
           <t>MLD</t>
         </is>
       </c>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="G18" s="115" t="n"/>
+      <c r="H18" s="115" t="inlineStr">
         <is>
           <t>COLC</t>
         </is>
       </c>
-      <c r="I18" s="13" t="inlineStr">
+      <c r="I18" s="68" t="inlineStr">
         <is>
           <t>2015-03-31</t>
         </is>
       </c>
-      <c r="J18" s="13" t="inlineStr">
+      <c r="J18" s="68" t="inlineStr">
         <is>
           <t>2015-04-04</t>
         </is>
       </c>
-      <c r="K18" s="11" t="inlineStr">
+      <c r="K18" s="115" t="inlineStr">
         <is>
           <t>TRAS. MAT.</t>
         </is>
       </c>
-      <c r="L18" s="14" t="n">
+      <c r="L18" s="117" t="n">
         <v>0</v>
       </c>
-      <c r="M18" s="15" t="n">
+      <c r="M18" s="118" t="n">
         <v>0</v>
       </c>
-      <c r="N18" s="11" t="inlineStr">
+      <c r="N18" s="115" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="O18" s="12" t="n">
+      <c r="O18" s="116" t="n">
         <v>2117994</v>
       </c>
-      <c r="P18" s="16" t="n">
+      <c r="P18" s="119" t="n">
         <v>-4.8</v>
       </c>
-      <c r="Q18" s="11" t="inlineStr">
+      <c r="Q18" s="115" t="inlineStr">
         <is>
           <t>LB</t>
         </is>
       </c>
-      <c r="R18" s="17" t="n">
+      <c r="R18" s="120" t="n">
         <v>5.72</v>
       </c>
-      <c r="S18" s="15" t="n">
+      <c r="S18" s="118" t="n">
         <v>-27.46</v>
       </c>
-      <c r="T18" s="16" t="n"/>
-      <c r="U18" s="15" t="n"/>
+      <c r="T18" s="119" t="n"/>
+      <c r="U18" s="118" t="n"/>
     </row>
     <row r="19" ht="15.95" customHeight="1" s="65">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="115" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="115" t="inlineStr">
         <is>
           <t>1000000.141000.CC</t>
         </is>
       </c>
-      <c r="C19" s="12" t="n">
+      <c r="C19" s="116" t="n">
         <v>34451021</v>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="115" t="inlineStr">
         <is>
           <t>IDM</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="115" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F19" s="115" t="inlineStr">
         <is>
           <t>MLD</t>
         </is>
       </c>
-      <c r="G19" s="11" t="n"/>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="G19" s="115" t="n"/>
+      <c r="H19" s="115" t="inlineStr">
         <is>
           <t>COLC</t>
         </is>
       </c>
-      <c r="I19" s="13" t="inlineStr">
+      <c r="I19" s="68" t="inlineStr">
         <is>
           <t>2015-03-19</t>
         </is>
       </c>
-      <c r="J19" s="13" t="inlineStr">
+      <c r="J19" s="68" t="inlineStr">
         <is>
           <t>2015-04-04</t>
         </is>
       </c>
-      <c r="K19" s="11" t="inlineStr">
+      <c r="K19" s="115" t="inlineStr">
         <is>
           <t>TRAS. MAT.</t>
         </is>
       </c>
-      <c r="L19" s="14" t="n">
+      <c r="L19" s="117" t="n">
         <v>4.8</v>
       </c>
-      <c r="M19" s="15" t="n">
+      <c r="M19" s="118" t="n">
         <v>27.46</v>
       </c>
-      <c r="N19" s="11" t="inlineStr">
+      <c r="N19" s="115" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="O19" s="12" t="n">
+      <c r="O19" s="116" t="n">
         <v>2110728</v>
       </c>
-      <c r="P19" s="16" t="n">
+      <c r="P19" s="119" t="n">
         <v>-20</v>
       </c>
-      <c r="Q19" s="11" t="inlineStr">
+      <c r="Q19" s="115" t="inlineStr">
         <is>
           <t>LB</t>
         </is>
       </c>
-      <c r="R19" s="17" t="n">
+      <c r="R19" s="120" t="n">
         <v>5.72</v>
       </c>
-      <c r="S19" s="15" t="n">
+      <c r="S19" s="118" t="n">
         <v>-114.4</v>
       </c>
-      <c r="T19" s="16" t="n"/>
-      <c r="U19" s="15" t="n"/>
+      <c r="T19" s="119" t="n"/>
+      <c r="U19" s="118" t="n"/>
     </row>
     <row r="20" ht="15.95" customHeight="1" s="65">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="115" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="115" t="inlineStr">
         <is>
           <t>1000000.141000.CC</t>
         </is>
       </c>
-      <c r="C20" s="19" t="n">
+      <c r="C20" s="116" t="n">
         <v>34448160</v>
       </c>
-      <c r="D20" s="18" t="inlineStr">
+      <c r="D20" s="115" t="inlineStr">
         <is>
           <t>IDM</t>
         </is>
       </c>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="E20" s="115" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="F20" s="18" t="inlineStr">
+      <c r="F20" s="115" t="inlineStr">
         <is>
           <t>MLD</t>
         </is>
       </c>
-      <c r="G20" s="18" t="n"/>
-      <c r="H20" s="18" t="inlineStr">
+      <c r="G20" s="115" t="n"/>
+      <c r="H20" s="115" t="inlineStr">
         <is>
           <t>COLC</t>
         </is>
       </c>
-      <c r="I20" s="20" t="inlineStr">
+      <c r="I20" s="68" t="inlineStr">
         <is>
           <t>2015-03-19</t>
         </is>
       </c>
-      <c r="J20" s="20" t="inlineStr">
+      <c r="J20" s="68" t="inlineStr">
         <is>
           <t>2015-04-04</t>
         </is>
       </c>
-      <c r="K20" s="18" t="inlineStr">
+      <c r="K20" s="115" t="inlineStr">
         <is>
           <t>TRAS. MAT.</t>
         </is>
       </c>
-      <c r="L20" s="21" t="n">
+      <c r="L20" s="117" t="n">
         <v>24.8</v>
       </c>
-      <c r="M20" s="22" t="n">
+      <c r="M20" s="118" t="n">
         <v>141.86</v>
       </c>
-      <c r="N20" s="18" t="inlineStr">
+      <c r="N20" s="115" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="O20" s="19" t="n">
+      <c r="O20" s="116" t="n">
         <v>2110708</v>
       </c>
-      <c r="P20" s="23" t="n">
+      <c r="P20" s="119" t="n">
         <v>20</v>
       </c>
-      <c r="Q20" s="18" t="inlineStr">
+      <c r="Q20" s="115" t="inlineStr">
         <is>
           <t>LB</t>
         </is>
       </c>
-      <c r="R20" s="24" t="n">
+      <c r="R20" s="120" t="n">
         <v>5.72</v>
       </c>
-      <c r="S20" s="22" t="n">
+      <c r="S20" s="118" t="n">
         <v>114.4</v>
       </c>
-      <c r="T20" s="23" t="n"/>
-      <c r="U20" s="22" t="n"/>
+      <c r="T20" s="119" t="n"/>
+      <c r="U20" s="118" t="n"/>
     </row>
     <row r="21" ht="15.95" customHeight="1" s="65">
-      <c r="A21" s="32" t="inlineStr">
+      <c r="A21" s="89" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B21" s="32" t="inlineStr">
+      <c r="B21" s="89" t="inlineStr">
         <is>
           <t>1000000.141000.CC</t>
         </is>
       </c>
-      <c r="C21" s="33" t="n">
+      <c r="C21" s="90" t="n">
         <v>34282449</v>
       </c>
-      <c r="D21" s="32" t="inlineStr">
+      <c r="D21" s="89" t="inlineStr">
         <is>
           <t>IDM</t>
         </is>
       </c>
-      <c r="E21" s="32" t="inlineStr">
+      <c r="E21" s="89" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="F21" s="32" t="inlineStr">
+      <c r="F21" s="89" t="inlineStr">
         <is>
           <t>MLD</t>
         </is>
       </c>
-      <c r="G21" s="32" t="n"/>
-      <c r="H21" s="32" t="inlineStr">
+      <c r="G21" s="89" t="n"/>
+      <c r="H21" s="89" t="inlineStr">
         <is>
           <t>COLC</t>
         </is>
       </c>
-      <c r="I21" s="34" t="inlineStr">
+      <c r="I21" s="91" t="inlineStr">
         <is>
           <t>2015-03-05</t>
         </is>
       </c>
-      <c r="J21" s="34" t="inlineStr">
+      <c r="J21" s="91" t="inlineStr">
         <is>
           <t>2015-04-04</t>
         </is>
       </c>
-      <c r="K21" s="32" t="inlineStr">
+      <c r="K21" s="89" t="inlineStr">
         <is>
           <t>Material C</t>
         </is>
       </c>
-      <c r="L21" s="35" t="n">
+      <c r="L21" s="92" t="n">
         <v>4.8</v>
       </c>
-      <c r="M21" s="36" t="n">
+      <c r="M21" s="93" t="n">
         <v>27.46</v>
       </c>
-      <c r="N21" s="32" t="inlineStr">
+      <c r="N21" s="89" t="inlineStr">
         <is>
           <t>IM</t>
         </is>
       </c>
-      <c r="O21" s="33" t="n">
+      <c r="O21" s="90" t="n">
         <v>1114048</v>
       </c>
-      <c r="P21" s="37" t="n">
+      <c r="P21" s="94" t="n">
         <v>-0.2</v>
       </c>
-      <c r="Q21" s="32" t="inlineStr">
+      <c r="Q21" s="89" t="inlineStr">
         <is>
           <t>LB</t>
         </is>
       </c>
-      <c r="R21" s="38" t="n">
+      <c r="R21" s="95" t="n">
         <v>5.72</v>
       </c>
-      <c r="S21" s="36" t="n">
+      <c r="S21" s="93" t="n">
         <v>-1.14</v>
       </c>
-      <c r="T21" s="37" t="n"/>
-      <c r="U21" s="36" t="n"/>
+      <c r="T21" s="94" t="n"/>
+      <c r="U21" s="93" t="n"/>
     </row>
     <row r="22" ht="15.95" customHeight="1" s="65">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="115" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="115" t="inlineStr">
         <is>
           <t>1000000.141000.CC</t>
         </is>
       </c>
-      <c r="C22" s="19" t="n">
+      <c r="C22" s="116" t="n">
         <v>34267218</v>
       </c>
-      <c r="D22" s="18" t="inlineStr">
+      <c r="D22" s="115" t="inlineStr">
         <is>
           <t>IDM</t>
         </is>
       </c>
-      <c r="E22" s="18" t="inlineStr">
+      <c r="E22" s="115" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="F22" s="18" t="inlineStr">
+      <c r="F22" s="115" t="inlineStr">
         <is>
           <t>MLD</t>
         </is>
       </c>
-      <c r="G22" s="18" t="n"/>
-      <c r="H22" s="18" t="inlineStr">
+      <c r="G22" s="115" t="n"/>
+      <c r="H22" s="115" t="inlineStr">
         <is>
           <t>COLC</t>
         </is>
       </c>
-      <c r="I22" s="20" t="inlineStr">
+      <c r="I22" s="68" t="inlineStr">
         <is>
           <t>2015-03-04</t>
         </is>
       </c>
-      <c r="J22" s="20" t="inlineStr">
+      <c r="J22" s="68" t="inlineStr">
         <is>
           <t>2015-04-04</t>
         </is>
       </c>
-      <c r="K22" s="18" t="inlineStr">
+      <c r="K22" s="115" t="inlineStr">
         <is>
           <t>TRAS. MAT.</t>
         </is>
       </c>
-      <c r="L22" s="21" t="n">
+      <c r="L22" s="117" t="n">
         <v>5</v>
       </c>
-      <c r="M22" s="22" t="n">
+      <c r="M22" s="118" t="n">
         <v>28.6</v>
       </c>
-      <c r="N22" s="18" t="inlineStr">
+      <c r="N22" s="115" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="O22" s="19" t="n">
+      <c r="O22" s="116" t="n">
         <v>2100212</v>
       </c>
-      <c r="P22" s="23" t="n">
+      <c r="P22" s="119" t="n">
         <v>5</v>
       </c>
-      <c r="Q22" s="18" t="inlineStr">
+      <c r="Q22" s="115" t="inlineStr">
         <is>
           <t>LB</t>
         </is>
       </c>
-      <c r="R22" s="24" t="n">
+      <c r="R22" s="120" t="n">
         <v>5.72</v>
       </c>
-      <c r="S22" s="22" t="n">
+      <c r="S22" s="118" t="n">
         <v>28.6</v>
       </c>
-      <c r="T22" s="23" t="n"/>
-      <c r="U22" s="22" t="n"/>
+      <c r="T22" s="119" t="n"/>
+      <c r="U22" s="118" t="n"/>
     </row>
     <row r="23" ht="15.95" customHeight="1" s="65">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="115" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="115" t="inlineStr">
         <is>
           <t>1000000.141000.CC</t>
         </is>
       </c>
-      <c r="C23" s="12" t="n">
+      <c r="C23" s="116" t="n">
         <v>34042358</v>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D23" s="115" t="inlineStr">
         <is>
           <t>IDM</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="115" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="F23" s="11" t="inlineStr">
+      <c r="F23" s="115" t="inlineStr">
         <is>
           <t>MLD</t>
         </is>
       </c>
-      <c r="G23" s="11" t="n"/>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="G23" s="115" t="n"/>
+      <c r="H23" s="115" t="inlineStr">
         <is>
           <t>COLC</t>
         </is>
       </c>
-      <c r="I23" s="13" t="inlineStr">
+      <c r="I23" s="68" t="inlineStr">
         <is>
           <t>2015-02-12</t>
         </is>
       </c>
-      <c r="J23" s="13" t="inlineStr">
+      <c r="J23" s="68" t="inlineStr">
         <is>
           <t>2015-02-28</t>
         </is>
       </c>
-      <c r="K23" s="11" t="inlineStr">
+      <c r="K23" s="115" t="inlineStr">
         <is>
           <t>CORR TASL.</t>
         </is>
       </c>
-      <c r="L23" s="14" t="n">
+      <c r="L23" s="117" t="n">
         <v>0</v>
       </c>
-      <c r="M23" s="15" t="n">
+      <c r="M23" s="118" t="n">
         <v>0</v>
       </c>
-      <c r="N23" s="11" t="inlineStr">
+      <c r="N23" s="115" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="O23" s="12" t="n">
+      <c r="O23" s="116" t="n">
         <v>2085838</v>
       </c>
-      <c r="P23" s="16" t="n">
+      <c r="P23" s="119" t="n">
         <v>-40</v>
       </c>
-      <c r="Q23" s="11" t="inlineStr">
+      <c r="Q23" s="115" t="inlineStr">
         <is>
           <t>LB</t>
         </is>
       </c>
-      <c r="R23" s="17" t="n">
+      <c r="R23" s="120" t="n">
         <v>5.72</v>
       </c>
-      <c r="S23" s="15" t="n">
+      <c r="S23" s="118" t="n">
         <v>-228.8</v>
       </c>
-      <c r="T23" s="16" t="n"/>
-      <c r="U23" s="15" t="n"/>
+      <c r="T23" s="119" t="n"/>
+      <c r="U23" s="118" t="n"/>
     </row>
     <row r="24" ht="15.95" customHeight="1" s="65">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="115" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B24" s="115" t="inlineStr">
         <is>
           <t>1000000.141000.CC</t>
         </is>
       </c>
-      <c r="C24" s="19" t="n">
+      <c r="C24" s="116" t="n">
         <v>34033620</v>
       </c>
-      <c r="D24" s="18" t="inlineStr">
+      <c r="D24" s="115" t="inlineStr">
         <is>
           <t>IDM</t>
         </is>
       </c>
-      <c r="E24" s="18" t="inlineStr">
+      <c r="E24" s="115" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="F24" s="18" t="inlineStr">
+      <c r="F24" s="115" t="inlineStr">
         <is>
           <t>MLD</t>
         </is>
       </c>
-      <c r="G24" s="18" t="n"/>
-      <c r="H24" s="18" t="inlineStr">
+      <c r="G24" s="115" t="n"/>
+      <c r="H24" s="115" t="inlineStr">
         <is>
           <t>COLC</t>
         </is>
       </c>
-      <c r="I24" s="20" t="inlineStr">
+      <c r="I24" s="68" t="inlineStr">
         <is>
           <t>2015-02-12</t>
         </is>
       </c>
-      <c r="J24" s="20" t="inlineStr">
+      <c r="J24" s="68" t="inlineStr">
         <is>
           <t>2015-02-28</t>
         </is>
       </c>
-      <c r="K24" s="18" t="inlineStr">
+      <c r="K24" s="115" t="inlineStr">
         <is>
           <t>WHS A MLD</t>
         </is>
       </c>
-      <c r="L24" s="21" t="n">
+      <c r="L24" s="117" t="n">
         <v>40</v>
       </c>
-      <c r="M24" s="22" t="n">
+      <c r="M24" s="118" t="n">
         <v>228.8</v>
       </c>
-      <c r="N24" s="18" t="inlineStr">
+      <c r="N24" s="115" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="O24" s="19" t="n">
+      <c r="O24" s="116" t="n">
         <v>2085546</v>
       </c>
-      <c r="P24" s="23" t="n">
+      <c r="P24" s="119" t="n">
         <v>40</v>
       </c>
-      <c r="Q24" s="18" t="inlineStr">
+      <c r="Q24" s="115" t="inlineStr">
         <is>
           <t>LB</t>
         </is>
       </c>
-      <c r="R24" s="24" t="n">
+      <c r="R24" s="120" t="n">
         <v>5.72</v>
       </c>
-      <c r="S24" s="22" t="n">
+      <c r="S24" s="118" t="n">
         <v>228.8</v>
       </c>
-      <c r="T24" s="23" t="n"/>
-      <c r="U24" s="22" t="n"/>
+      <c r="T24" s="119" t="n"/>
+      <c r="U24" s="118" t="n"/>
     </row>
     <row r="25" ht="15.95" customHeight="1" s="65">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="107" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="107" t="inlineStr">
         <is>
           <t>1000000.141000.CC</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="C25" s="108" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="107" t="inlineStr">
         <is>
           <t>IDM</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="107" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="107" t="inlineStr">
         <is>
           <t>MLD</t>
         </is>
       </c>
-      <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G25" s="107" t="n"/>
+      <c r="H25" s="107" t="inlineStr">
         <is>
           <t>COLC</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="I25" s="52" t="inlineStr">
         <is>
           <t>2015-08-30</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="J25" s="52" t="inlineStr">
         <is>
           <t>2015-08-30</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="K25" s="107" t="inlineStr">
         <is>
           <t>Beg bal</t>
         </is>
       </c>
-      <c r="L25" s="5" t="n">
+      <c r="L25" s="109" t="n">
         <v>0</v>
       </c>
-      <c r="M25" s="6" t="n">
+      <c r="M25" s="110" t="n">
         <v>0</v>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="N25" s="107" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O25" s="3" t="n"/>
-      <c r="P25" s="7" t="n">
+      <c r="O25" s="108" t="n"/>
+      <c r="P25" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" s="2" t="inlineStr">
+      <c r="Q25" s="107" t="inlineStr">
         <is>
           <t>LB</t>
         </is>
       </c>
-      <c r="R25" s="8" t="n">
+      <c r="R25" s="112" t="n">
         <v>0</v>
       </c>
-      <c r="S25" s="6" t="n">
+      <c r="S25" s="110" t="n">
         <v>0</v>
       </c>
-      <c r="T25" s="7" t="n"/>
-      <c r="U25" s="6" t="n"/>
-    </row>
-    <row r="26"/>
-    <row r="27"/>
+      <c r="T25" s="111" t="n"/>
+      <c r="U25" s="110" t="n"/>
+    </row>
     <row r="28">
       <c r="A28" s="69" t="inlineStr">
         <is>
@@ -2844,7 +3666,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="46" t="n"/>
+      <c r="A29" s="121" t="n"/>
       <c r="B29" s="68" t="inlineStr">
         <is>
           <t>Curr bal (cost method 07, cost level 2) and Beg bal</t>
@@ -2864,7 +3686,7 @@
       <c r="D30" s="78" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="48" t="n"/>
+      <c r="A31" s="121" t="n"/>
       <c r="B31" s="68" t="inlineStr">
         <is>
           <t>Related — negative IA adjustments (Oct 2015)</t>
@@ -2874,7 +3696,7 @@
       <c r="D31" s="78" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="49" t="n"/>
+      <c r="A32" s="121" t="n"/>
       <c r="B32" s="68" t="inlineStr">
         <is>
           <t>IT transfers in (positive qty)</t>
@@ -2884,7 +3706,7 @@
       <c r="D32" s="78" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="50" t="n"/>
+      <c r="A33" s="121" t="n"/>
       <c r="B33" s="68" t="inlineStr">
         <is>
           <t>IT transfers out (negative qty)</t>
@@ -2894,7 +3716,7 @@
       <c r="D33" s="78" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="51" t="n"/>
+      <c r="A34" s="103" t="n"/>
       <c r="B34" s="68" t="inlineStr">
         <is>
           <t>IM material issues to work orders</t>
@@ -2917,740 +3739,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B70"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" style="65" min="1" max="1"/>
-    <col width="52" bestFit="1" customWidth="1" style="65" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="42" customHeight="1" s="65">
-      <c r="A1" s="80" t="inlineStr">
-        <is>
-          <t>RR Analysis — Standard Cost (Method 07) Quantity &amp; Amount Variance</t>
-        </is>
-      </c>
-      <c r="B1" s="81" t="n"/>
-    </row>
-    <row r="2" ht="16" customHeight="1" s="65">
-      <c r="A2" s="81" t="n"/>
-      <c r="B2" s="81" t="n"/>
-    </row>
-    <row r="3" ht="16" customHeight="1" s="65">
-      <c r="A3" s="82" t="inlineStr">
-        <is>
-          <t>DOCUMENT</t>
-        </is>
-      </c>
-      <c r="B3" s="81" t="n"/>
-    </row>
-    <row r="4" ht="16" customHeight="1" s="65">
-      <c r="A4" s="83" t="inlineStr">
-        <is>
-          <t>Item Number</t>
-        </is>
-      </c>
-      <c r="B4" s="53" t="inlineStr">
-        <is>
-          <t>555</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1" s="65">
-      <c r="A5" s="83" t="inlineStr">
-        <is>
-          <t>Lot</t>
-        </is>
-      </c>
-      <c r="B5" s="53" t="inlineStr">
-        <is>
-          <t>(none — no lot assigned)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1" s="65">
-      <c r="A6" s="83" t="inlineStr">
-        <is>
-          <t>Branch</t>
-        </is>
-      </c>
-      <c r="B6" s="53" t="inlineStr">
-        <is>
-          <t>IDM</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1" s="65">
-      <c r="A7" s="83" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="B7" s="53" t="inlineStr">
-        <is>
-          <t>MLD</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1" s="65">
-      <c r="A8" s="83" t="inlineStr">
-        <is>
-          <t>GL Account</t>
-        </is>
-      </c>
-      <c r="B8" s="53" t="inlineStr">
-        <is>
-          <t>1000000.141000.CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1" s="65">
-      <c r="A9" s="83" t="inlineStr">
-        <is>
-          <t>GL Class</t>
-        </is>
-      </c>
-      <c r="B9" s="53" t="inlineStr">
-        <is>
-          <t>COLC</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1" s="65">
-      <c r="A10" s="83" t="inlineStr">
-        <is>
-          <t>UOM</t>
-        </is>
-      </c>
-      <c r="B10" s="53" t="inlineStr">
-        <is>
-          <t>LB</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1" s="65">
-      <c r="A11" s="83" t="inlineStr">
-        <is>
-          <t>Analysis Date</t>
-        </is>
-      </c>
-      <c r="B11" s="53" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" s="65">
-      <c r="A12" s="84" t="inlineStr">
-        <is>
-          <t>QtyVar</t>
-        </is>
-      </c>
-      <c r="B12" s="84" t="inlineStr">
-        <is>
-          <t>+10.35 LB  (F4111 ledger exceeds F41021 on-hand by 10.35 LB)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1" s="65">
-      <c r="A13" s="84" t="inlineStr">
-        <is>
-          <t>AmtVar</t>
-        </is>
-      </c>
-      <c r="B13" s="84" t="inlineStr">
-        <is>
-          <t>+$59.15</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1" s="65">
-      <c r="A14" s="81" t="n"/>
-      <c r="B14" s="81" t="n"/>
-    </row>
-    <row r="15" ht="42" customHeight="1" s="65">
-      <c r="A15" s="82" t="inlineStr">
-        <is>
-          <t>COST METHOD  (dt field, ukid = 999999999999 — Curr bal row)</t>
-        </is>
-      </c>
-      <c r="B15" s="81" t="n"/>
-    </row>
-    <row r="16" ht="16" customHeight="1" s="65">
-      <c r="A16" s="57" t="inlineStr">
-        <is>
-          <t>Cost Method Code</t>
-        </is>
-      </c>
-      <c r="B16" s="57" t="inlineStr">
-        <is>
-          <t>07 — Standard Cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1" s="65">
-      <c r="A17" s="83" t="inlineStr">
-        <is>
-          <t>Standard cost</t>
-        </is>
-      </c>
-      <c r="B17" s="53" t="inlineStr">
-        <is>
-          <t>$5.72/LB (frozen in F4105, method 07) — consistent across all 21 transactions</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="98" customHeight="1" s="65">
-      <c r="A18" s="83" t="inlineStr">
-        <is>
-          <t>Implications</t>
-        </is>
-      </c>
-      <c r="B18" s="53" t="inlineStr">
-        <is>
-          <t>Costs are frozen from F30026 cost components. Key risks: (1) component/ledger mismatch — run R30543 or RR Integrity Report 6 to confirm F4105 method 07 equals sum of F30026 components; (2) WIP Revaluation — if standard cost was updated after open work orders were created, R30837 must be run from R30835 to revalue WIP.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="84" customHeight="1" s="65">
-      <c r="A19" s="83" t="inlineStr">
-        <is>
-          <t>Cost integrity check</t>
-        </is>
-      </c>
-      <c r="B19" s="53" t="inlineStr">
-        <is>
-          <t>Single standard cost of $5.72/LB observed throughout all transactions. No cost drift detected. F4111 value (runamt $59.21) = runqty (10.35) × std cost ($5.72) = $59.202 — consistent with standard cost behaviour. Component/ledger mismatch is not the primary cause of this variance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1" s="65">
-      <c r="A20" s="81" t="n"/>
-      <c r="B20" s="81" t="n"/>
-    </row>
-    <row r="21" ht="28" customHeight="1" s="65">
-      <c r="A21" s="82" t="inlineStr">
-        <is>
-          <t>COST LEVEL  (dt field, ukid = 0 — Beg bal row)</t>
-        </is>
-      </c>
-      <c r="B21" s="81" t="n"/>
-    </row>
-    <row r="22" ht="16" customHeight="1" s="65">
-      <c r="A22" s="57" t="inlineStr">
-        <is>
-          <t>Cost Level Code</t>
-        </is>
-      </c>
-      <c r="B22" s="57" t="inlineStr">
-        <is>
-          <t>2 — Item/Branch level</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="56" customHeight="1" s="65">
-      <c r="A23" s="83" t="inlineStr">
-        <is>
-          <t>Reconciliation scope</t>
-        </is>
-      </c>
-      <c r="B23" s="53" t="inlineStr">
-        <is>
-          <t>F4111 summary and F41021 comparison performed at item/branch level, inclusive of all locations and lots. Location MLD is the only location present — no cross-location aggregation issues.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1" s="65">
-      <c r="A24" s="81" t="n"/>
-      <c r="B24" s="81" t="n"/>
-    </row>
-    <row r="25" ht="28" customHeight="1" s="65">
-      <c r="A25" s="82" t="inlineStr">
-        <is>
-          <t>BEGINNING BALANCE  (ukid = 0 — Beg bal row)</t>
-        </is>
-      </c>
-      <c r="B25" s="81" t="n"/>
-    </row>
-    <row r="26" ht="16" customHeight="1" s="65">
-      <c r="A26" s="83" t="inlineStr">
-        <is>
-          <t>Beg bal date</t>
-        </is>
-      </c>
-      <c r="B26" s="53" t="inlineStr">
-        <is>
-          <t>2015-08-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1" s="65">
-      <c r="A27" s="85" t="inlineStr">
-        <is>
-          <t>Beg bal qty</t>
-        </is>
-      </c>
-      <c r="B27" s="58" t="inlineStr">
-        <is>
-          <t>0.00 LB — zero opening balance</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1" s="65">
-      <c r="A28" s="83" t="inlineStr">
-        <is>
-          <t>Beg bal amount</t>
-        </is>
-      </c>
-      <c r="B28" s="53" t="inlineStr">
-        <is>
-          <t>$0.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="84" customHeight="1" s="65">
-      <c r="A29" s="83" t="inlineStr">
-        <is>
-          <t>Beg bal integrity</t>
-        </is>
-      </c>
-      <c r="B29" s="53" t="inlineStr">
-        <is>
-          <t>PASS — Beg bal (0.00 LB) + net transactions (+10.35 LB) = Curr bal runqty (10.35 LB). F4111 ledger is internally consistent. The entire on-hand balance was built from transactions after RR go-live; the beginning balance itself is not the source of the variance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1" s="65">
-      <c r="A30" s="81" t="n"/>
-      <c r="B30" s="81" t="n"/>
-    </row>
-    <row r="31" ht="28" customHeight="1" s="65">
-      <c r="A31" s="82" t="inlineStr">
-        <is>
-          <t>TRANSACTION SUMMARY (2015-02-12 to 2016-08-08)</t>
-        </is>
-      </c>
-      <c r="B31" s="81" t="n"/>
-    </row>
-    <row r="32" ht="28" customHeight="1" s="65">
-      <c r="A32" s="86" t="inlineStr">
-        <is>
-          <t>IT (transfers)</t>
-        </is>
-      </c>
-      <c r="B32" s="60" t="inlineStr">
-        <is>
-          <t>15 transactions  |  Net qty: +4.900 LB  |  Net val: +$28.03</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="28" customHeight="1" s="65">
-      <c r="A33" s="84" t="inlineStr">
-        <is>
-          <t>IA (adjustments)</t>
-        </is>
-      </c>
-      <c r="B33" s="87" t="inlineStr">
-        <is>
-          <t>4 transactions   |  Net qty: +9.970 LB  |  Net val: +$57.03</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1" s="65">
-      <c r="A34" s="88" t="inlineStr">
-        <is>
-          <t>IM (WO issues)</t>
-        </is>
-      </c>
-      <c r="B34" s="63" t="inlineStr">
-        <is>
-          <t>2 transactions   |  Net qty: –4.520 LB  |  Net val: –$25.85</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="28" customHeight="1" s="65">
-      <c r="A35" s="83" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B35" s="53" t="inlineStr">
-        <is>
-          <t>Net qty: +10.350 LB  |  Net val: +$59.21  ✓  ties to Curr bal runqty and runamt</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="16" customHeight="1" s="65">
-      <c r="A36" s="81" t="n"/>
-      <c r="B36" s="81" t="n"/>
-    </row>
-    <row r="37" ht="16" customHeight="1" s="65">
-      <c r="A37" s="82" t="inlineStr">
-        <is>
-          <t>AMTVAR DECOMPOSITION</t>
-        </is>
-      </c>
-      <c r="B37" s="81" t="n"/>
-    </row>
-    <row r="38" ht="28" customHeight="1" s="65">
-      <c r="A38" s="84" t="inlineStr">
-        <is>
-          <t>QtyVar × std cost</t>
-        </is>
-      </c>
-      <c r="B38" s="87" t="inlineStr">
-        <is>
-          <t>+10.35 LB × $5.72 = $59.202  (Component A — resolved by correcting the quantity gap)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="28" customHeight="1" s="65">
-      <c r="A39" s="83" t="inlineStr">
-        <is>
-          <t>Residual dollar-only</t>
-        </is>
-      </c>
-      <c r="B39" s="53" t="inlineStr">
-        <is>
-          <t>$59.15 – $59.202 = –$0.052  (Component B — immaterial rounding, no separate IA required)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1" s="65">
-      <c r="A40" s="81" t="n"/>
-      <c r="B40" s="81" t="n"/>
-    </row>
-    <row r="41" ht="16" customHeight="1" s="65">
-      <c r="A41" s="82" t="inlineStr">
-        <is>
-          <t>ROOT CAUSE</t>
-        </is>
-      </c>
-      <c r="B41" s="81" t="n"/>
-    </row>
-    <row r="42" ht="56" customHeight="1" s="65">
-      <c r="A42" s="83" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B42" s="53" t="inlineStr">
-        <is>
-          <t>Section 4h — F41021 vs F4111 Integrity Gap (Quantity Variance). QtyVar = +10.35 LB; F4111 ledger is internally consistent; standard cost is stable throughout — WAC escalation is not a factor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="56" customHeight="1" s="65">
-      <c r="A43" s="84" t="inlineStr">
-        <is>
-          <t>Key finding</t>
-        </is>
-      </c>
-      <c r="B43" s="84" t="inlineStr">
-        <is>
-          <t>Curr bal runqty (10.35 LB) = QtyVar (10.35 LB). This means F41021 on-hand = 0 LB while F4111 records 10.35 LB. The entire current ledger balance is the variance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="112" customHeight="1" s="65">
-      <c r="A44" s="84" t="inlineStr">
-        <is>
-          <t>Primary suspect — IA doc 167759</t>
-        </is>
-      </c>
-      <c r="B44" s="87" t="inlineStr">
-        <is>
-          <t>A single positive IA transaction (doc 167759, 'MAT. SOBR.', 2016-06-10) added +15.62 LB to F4111. The three prior negative IAs (Oct 2015) totalling –5.65 LB brought the balance to zero, after which this large positive IA is the sole source of the current 10.35 LB ledger balance. If this IA posted to F4111 but failed to update F41021, it fully explains the variance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="84" customHeight="1" s="65">
-      <c r="A45" s="83" t="inlineStr">
-        <is>
-          <t>Post-IA IT activity</t>
-        </is>
-      </c>
-      <c r="B45" s="53" t="inlineStr">
-        <is>
-          <t>After the Jun 2016 IA, five IT transfers moved inventory in and out, netting –5.27 LB (15.62 – 5.27 = 10.35 LB current balance). If F41021 was zero throughout, these IT transactions also failed to update F41021, which is consistent with F41021 being stale since the missed IA posting.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="16" customHeight="1" s="65">
-      <c r="A46" s="81" t="n"/>
-      <c r="B46" s="81" t="n"/>
-    </row>
-    <row r="47" ht="28" customHeight="1" s="65">
-      <c r="A47" s="82" t="inlineStr">
-        <is>
-          <t>EVIDENCE — SOURCE ROWS (Sheet: Item Roll Forward)</t>
-        </is>
-      </c>
-      <c r="B47" s="81" t="n"/>
-    </row>
-    <row r="48" ht="28" customHeight="1" s="65">
-      <c r="A48" s="83" t="inlineStr">
-        <is>
-          <t>Curr bal row</t>
-        </is>
-      </c>
-      <c r="B48" s="53" t="inlineStr">
-        <is>
-          <t>Excel row 3 — runqty=10.35, runamt=$59.21, qtyvar=10.35, amtvar=$59.15  (AMBER)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="28" customHeight="1" s="65">
-      <c r="A49" s="83" t="inlineStr">
-        <is>
-          <t>IA doc 167759</t>
-        </is>
-      </c>
-      <c r="B49" s="53" t="inlineStr">
-        <is>
-          <t>Excel row 5 — +15.62 LB IA 'MAT. SOBR.' 2016-06-10  (RED — root cause)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="28" customHeight="1" s="65">
-      <c r="A50" s="83" t="inlineStr">
-        <is>
-          <t>Negative IA rows</t>
-        </is>
-      </c>
-      <c r="B50" s="53" t="inlineStr">
-        <is>
-          <t>Excel rows 9–11 — three IAs Oct 2015 totalling –5.65 LB  (ORANGE — related)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="16" customHeight="1" s="65">
-      <c r="A51" s="83" t="inlineStr">
-        <is>
-          <t>Beg bal row</t>
-        </is>
-      </c>
-      <c r="B51" s="53" t="inlineStr">
-        <is>
-          <t>Excel row 23 — runqty=0.00, runamt=$0.00  (AMBER)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="16" customHeight="1" s="65">
-      <c r="A52" s="81" t="n"/>
-      <c r="B52" s="81" t="n"/>
-    </row>
-    <row r="53" ht="16" customHeight="1" s="65">
-      <c r="A53" s="82" t="inlineStr">
-        <is>
-          <t>CORRECTIVE ACTION — JDE</t>
-        </is>
-      </c>
-      <c r="B53" s="81" t="n"/>
-    </row>
-    <row r="54" ht="42" customHeight="1" s="65">
-      <c r="A54" s="83" t="inlineStr">
-        <is>
-          <t>Step 1 — Validate qty</t>
-        </is>
-      </c>
-      <c r="B54" s="53" t="inlineStr">
-        <is>
-          <t>Confirm F41021 on-hand qty = 0 LB for Item 555 / Branch IDM / Location MLD. If F41021 shows a non-zero value, re-scope the investigation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="56" customHeight="1" s="65">
-      <c r="A55" s="83" t="inlineStr">
-        <is>
-          <t>Step 2 — Check for unposted IA</t>
-        </is>
-      </c>
-      <c r="B55" s="53" t="inlineStr">
-        <is>
-          <t>Query F4111 for Item 555 / Branch IDM. Filter IA rows for ILIPCD ≠ 'P'. Focus on doc 167759 (2016-06-10, +15.62 LB). Also check GL Batches variance in RapidReconciler for outstanding unposted IA batches.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="42" customHeight="1" s="65">
-      <c r="A56" s="83" t="inlineStr">
-        <is>
-          <t>Step 3a — If unposted batch found</t>
-        </is>
-      </c>
-      <c r="B56" s="53" t="inlineStr">
-        <is>
-          <t>Post the batch in JD Edwards. Recheck F41021 qty after posting. If F41021 updates to 10.35 LB, the variance is resolved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="56" customHeight="1" s="65">
-      <c r="A57" s="83" t="inlineStr">
-        <is>
-          <t>Step 3b — If all batches posted</t>
-        </is>
-      </c>
-      <c r="B57" s="53" t="inlineStr">
-        <is>
-          <t>F41021 did not update when the IA processed. Request an F41021 SQL correction from IT for +10.35 LB. DBA support required. Confirm F4111 is the accurate record before proceeding.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="70" customHeight="1" s="65">
-      <c r="A58" s="83" t="inlineStr">
-        <is>
-          <t>Step 4 — Standard cost check</t>
-        </is>
-      </c>
-      <c r="B58" s="53" t="inlineStr">
-        <is>
-          <t>Run R30543 or RR Integrity Report 6 to confirm F4105 method 07 ($5.72/LB) equals the sum of F30026 cost components. Consistent standard cost observed here makes a component/ledger mismatch unlikely, but this should be confirmed before closing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="28" customHeight="1" s="65">
-      <c r="A59" s="83" t="inlineStr">
-        <is>
-          <t>Step 5 — Dollar residual</t>
-        </is>
-      </c>
-      <c r="B59" s="53" t="inlineStr">
-        <is>
-          <t>Component B residual = –$0.052. Immaterial — no separate dollars-only IA required.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="56" customHeight="1" s="65">
-      <c r="A60" s="83" t="inlineStr">
-        <is>
-          <t>Step 6 — Re-Roll in RapidReconciler</t>
-        </is>
-      </c>
-      <c r="B60" s="53" t="inlineStr">
-        <is>
-          <t>After JDE correction, open Re-Roll Item dialog for Item 555. Select Re-Roll Item. Verify details. Click Re-Roll. Confirm QtyVar = 0 and AmtVar = 0 after next nightly refresh.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="16" customHeight="1" s="65">
-      <c r="A61" s="81" t="n"/>
-      <c r="B61" s="81" t="n"/>
-    </row>
-    <row r="62" ht="16" customHeight="1" s="65">
-      <c r="A62" s="82" t="inlineStr">
-        <is>
-          <t>PREVENTIVE ACTIONS</t>
-        </is>
-      </c>
-      <c r="B62" s="81" t="n"/>
-    </row>
-    <row r="63" ht="56" customHeight="1" s="65">
-      <c r="A63" s="83" t="inlineStr">
-        <is>
-          <t>1 — IA batch posting controls</t>
-        </is>
-      </c>
-      <c r="B63" s="53" t="inlineStr">
-        <is>
-          <t>Confirm all IA batches for Branch IDM auto-approve and auto-post. A single large positive IA (+15.62 LB) that failed to update F41021 is the likely origin of this variance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="42" customHeight="1" s="65">
-      <c r="A64" s="83" t="inlineStr">
-        <is>
-          <t>2 — R30543 periodic review</t>
-        </is>
-      </c>
-      <c r="B64" s="53" t="inlineStr">
-        <is>
-          <t>Run R30543 (or use RR Integrity Report 6) before each period-end close to proactively identify standard cost component/ledger mismatches.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="56" customHeight="1" s="65">
-      <c r="A65" s="83" t="inlineStr">
-        <is>
-          <t>3 — WIP Revaluation monitoring</t>
-        </is>
-      </c>
-      <c r="B65" s="53" t="inlineStr">
-        <is>
-          <t>If the $5.72/LB standard cost is updated in future, ensure R30837 is invoked from R30835 to revalue any open work orders. Failure to do so will leave WIP at the old standard.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="16" customHeight="1" s="65">
-      <c r="A66" s="81" t="n"/>
-      <c r="B66" s="81" t="n"/>
-    </row>
-    <row r="67" ht="28" customHeight="1" s="65">
-      <c r="A67" s="82" t="inlineStr">
-        <is>
-          <t>OPEN ITEMS REQUIRING JDE INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="B67" s="81" t="n"/>
-    </row>
-    <row r="68" ht="28" customHeight="1" s="65">
-      <c r="A68" s="83" t="inlineStr">
-        <is>
-          <t>?  F41021 current QOH</t>
-        </is>
-      </c>
-      <c r="B68" s="53" t="inlineStr">
-        <is>
-          <t>Confirm F41021 on-hand = 0 LB before posting any correction — cannot verify from Excel alone</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="28" customHeight="1" s="65">
-      <c r="A69" s="83" t="inlineStr">
-        <is>
-          <t>?  IA doc 167759 posting status</t>
-        </is>
-      </c>
-      <c r="B69" s="53" t="inlineStr">
-        <is>
-          <t>Query ILIPCD on this F4111 row — determine whether it posted correctly or failed to update F41021</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="28" customHeight="1" s="65">
-      <c r="A70" s="83" t="inlineStr">
-        <is>
-          <t>?  R30543 / Integrity Report 6</t>
-        </is>
-      </c>
-      <c r="B70" s="53" t="inlineStr">
-        <is>
-          <t>Confirm no component/ledger mismatch exists for Item 555 at current standard cost $5.72/LB</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A53:B53"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/Analysis Examples/Cardex-Variance-Item-Analysis.xlsx
+++ b/Analysis Examples/Cardex-Variance-Item-Analysis.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.000;\(#,##0.000\);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,6 +75,23 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -227,7 +244,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -568,6 +585,15 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -642,6 +668,241 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1001" name="RR Note"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="91440" rIns="91440" tIns="45720" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l">
+            <a:spcAft>
+              <a:spcPts val="300"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:t>Cardex Variance Analysis</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l">
+            <a:spcBef>
+              <a:spcPts val="400"/>
+            </a:spcBef>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l">
+            <a:spcAft>
+              <a:spcPts val="300"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1300" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:t>What is a Cardex Variance?</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:t>A Cardex (Item Roll Forward) records every inventory movement for an item with running quantity and amount balances. A variance exists when the running amount does not agree with the expected value for the on-hand quantity. This compares the item ledger F4111 to the item balance F41021.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l">
+            <a:spcBef>
+              <a:spcPts val="400"/>
+            </a:spcBef>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l">
+            <a:spcAft>
+              <a:spcPts val="300"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1300" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:t>Why does it matter?</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:t>The most critical scenario is quantity = zero but a residual dollar balance remains — a stranded amount sitting on the inventory GL account that will persist until corrected.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l">
+            <a:spcBef>
+              <a:spcPts val="400"/>
+            </a:spcBef>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l">
+            <a:spcAft>
+              <a:spcPts val="300"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1300" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:t>What does this workbook show?</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:t>This analysis traces the root cause for a specific item, identifies the exact transaction and cost that created the imbalance, and provides the corrective action steps in JD Edwards.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l">
+            <a:spcBef>
+              <a:spcPts val="400"/>
+            </a:spcBef>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l">
+            <a:spcAft>
+              <a:spcPts val="300"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1300" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:t>About this workbook</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:t>RR Analysis = findings and recommended actions. Item Roll Forward = source export data.</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -933,32 +1194,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B70"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" style="65" min="1" max="1"/>
     <col width="52" bestFit="1" customWidth="1" style="65" min="2" max="2"/>
+    <col width="8" customWidth="1" style="65" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="42" customHeight="1" s="65">
+    <row r="1" ht="20" customHeight="1" s="65">
       <c r="A1" s="80" t="inlineStr">
         <is>
           <t>RR Analysis — Standard Cost (Method 07) Quantity &amp; Amount Variance</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="16" customHeight="1" s="65">
+      <c r="F1" s="122" t="n"/>
+    </row>
+    <row r="2" s="65">
       <c r="A2" s="81" t="n"/>
       <c r="B2" s="81" t="n"/>
-    </row>
-    <row r="3" ht="16" customHeight="1" s="65">
+      <c r="F2" s="123" t="n"/>
+    </row>
+    <row r="3" s="65">
       <c r="A3" s="82" t="inlineStr">
         <is>
           <t>DOCUMENT</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="16" customHeight="1" s="65">
+      <c r="F3" s="124" t="n"/>
+    </row>
+    <row r="4" ht="42" customHeight="1" s="65">
       <c r="A4" s="83" t="inlineStr">
         <is>
           <t>Item Number</t>
@@ -969,8 +1234,9 @@
           <t>555</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="16" customHeight="1" s="65">
+      <c r="F4" s="123" t="n"/>
+    </row>
+    <row r="5" s="65">
       <c r="A5" s="83" t="inlineStr">
         <is>
           <t>Lot</t>
@@ -981,8 +1247,9 @@
           <t>(none — no lot assigned)</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="16" customHeight="1" s="65">
+      <c r="F5" s="123" t="n"/>
+    </row>
+    <row r="6" s="65">
       <c r="A6" s="83" t="inlineStr">
         <is>
           <t>Branch</t>
@@ -993,8 +1260,9 @@
           <t>IDM</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="16" customHeight="1" s="65">
+      <c r="F6" s="124" t="n"/>
+    </row>
+    <row r="7" ht="42" customHeight="1" s="65">
       <c r="A7" s="83" t="inlineStr">
         <is>
           <t>Location</t>
@@ -1005,8 +1273,9 @@
           <t>MLD</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="16" customHeight="1" s="65">
+      <c r="F7" s="123" t="n"/>
+    </row>
+    <row r="8" s="65">
       <c r="A8" s="83" t="inlineStr">
         <is>
           <t>GL Account</t>
@@ -1017,8 +1286,9 @@
           <t>1000000.141000.CC</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="16" customHeight="1" s="65">
+      <c r="F8" s="123" t="n"/>
+    </row>
+    <row r="9" s="65">
       <c r="A9" s="83" t="inlineStr">
         <is>
           <t>GL Class</t>
@@ -1029,8 +1299,9 @@
           <t>COLC</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="16" customHeight="1" s="65">
+      <c r="F9" s="124" t="n"/>
+    </row>
+    <row r="10" ht="42" customHeight="1" s="65">
       <c r="A10" s="83" t="inlineStr">
         <is>
           <t>UOM</t>
@@ -1041,8 +1312,9 @@
           <t>LB</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="16" customHeight="1" s="65">
+      <c r="F10" s="123" t="n"/>
+    </row>
+    <row r="11" s="65">
       <c r="A11" s="83" t="inlineStr">
         <is>
           <t>Analysis Date</t>
@@ -1053,8 +1325,9 @@
           <t>2026-04-21</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" s="65">
+      <c r="F11" s="123" t="n"/>
+    </row>
+    <row r="12" s="65">
       <c r="A12" s="84" t="inlineStr">
         <is>
           <t>QtyVar</t>
@@ -1065,8 +1338,9 @@
           <t>+10.35 LB  (F4111 ledger exceeds F41021 on-hand by 10.35 LB)</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="16" customHeight="1" s="65">
+      <c r="F12" s="124" t="n"/>
+    </row>
+    <row r="13" ht="42" customHeight="1" s="65">
       <c r="A13" s="84" t="inlineStr">
         <is>
           <t>AmtVar</t>
@@ -1077,8 +1351,9 @@
           <t>+$59.15</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="16" customHeight="1" s="65">
+      <c r="F13" s="123" t="n"/>
+    </row>
+    <row r="14" s="65">
       <c r="A14" s="81" t="n"/>
       <c r="B14" s="81" t="n"/>
     </row>
@@ -1089,7 +1364,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="16" customHeight="1" s="65">
+    <row r="16" s="65">
       <c r="A16" s="104" t="inlineStr">
         <is>
           <t>Cost Method Code</t>
@@ -1648,6 +1923,7 @@
     <mergeCell ref="A53:B53"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId100"/>
 </worksheet>
 </file>
 

--- a/Analysis Examples/Cardex-Variance-Item-Analysis.xlsx
+++ b/Analysis Examples/Cardex-Variance-Item-Analysis.xlsx
@@ -1531,7 +1531,7 @@
     <row r="2" ht="38" customHeight="1" s="65">
       <c r="A2" s="126" t="inlineStr">
         <is>
-          <t>Item 555 — Branch IDM, Location MLD</t>
+          <t>Item 99955 — Branch BR1, Location LOC1</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
     <row r="4" ht="18" customHeight="1" s="65">
       <c r="A4" s="128" t="inlineStr">
         <is>
-          <t>GL Class  COLC          GL Account  1000000.141000.CC          Std Cost  $5.72/LB</t>
+          <t>GL Class  COLC          GL Account  9100000.611000.A1          Std Cost  $5.72/LB</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
     <row r="10" ht="130" customHeight="1" s="65">
       <c r="A10" s="134" t="inlineStr">
         <is>
-          <t>The F4111 item ledger for Item 555 shows a current running balance of 10.35 LB worth $59.21 — but RapidReconciler reports the F41021 on-hand table is 10.35 LB short.
+          <t>The F4111 item ledger for Item 99955 shows a current running balance of 10.35 LB worth $59.21 — but RapidReconciler reports the F41021 on-hand table is 10.35 LB short.
 The entire current ledger balance is the variance: F41021 is effectively at 0 LB while F4111 says 10.35 LB.  Standard cost has held steady at $5.72/LB throughout, so the dollar gap is essentially the quantity gap × standard cost.  Fixing the quantity will clear most of the dollar variance, with a small residual to clean up.</t>
         </is>
       </c>
@@ -1625,11 +1625,11 @@
     <row r="14" ht="240" customHeight="1" s="65">
       <c r="A14" s="134" t="inlineStr">
         <is>
-          <t>Step 1.  Confirm F41021 on-hand qty for Item 555 / Branch IDM / Location MLD really is 0 LB.  If it isn’t, run a cycle count or adjust the quantity manually, then re-evaluate after the next RapidReconciler refresh cycle.
+          <t>Step 1.  Confirm F41021 on-hand qty for Item 99955 / Branch BR1 / Location LOC1 really is 0 LB.  If it isn’t, run a cycle count or adjust the quantity manually, then re-evaluate after the next RapidReconciler refresh cycle.
 Step 2.  View the item on the item ledger screen in JD Edwards, display all rows, and export to Excel.  Then perform an analysis using the “Handling Cardex Variance Guide” to obtain the current quantity and amount variances — these are the figures to use for the corrections in the steps below, since the variance shown here may have moved since this analysis was generated.
 Step 3.  Request an F41021 SQL correction from IT using the current quantity variance from Step 2 (DBA support required — confirm F4111 is the accurate record before proceeding).
 Step 4.  If there are any residual amounts after the quantity correction, perform a dollars-only adjustment to clear.
-Step 5.  After the corrections, run Re-Roll on the RapidReconciler As Of page for all locations for Item 555 and confirm QtyVar and AmtVar both go to zero on the next refresh.</t>
+Step 5.  After the corrections, run Re-Roll on the RapidReconciler As Of page for all locations for Item 99955 and confirm QtyVar and AmtVar both go to zero on the next refresh.</t>
         </is>
       </c>
       <c r="B14" s="135" t="n"/>
@@ -1870,7 +1870,7 @@
     <row r="1" ht="27.95" customHeight="1" s="65">
       <c r="A1" s="67" t="inlineStr">
         <is>
-          <t>Item Roll Forward — Item 555 / Branch IDM / Location MLD  |  Cost Method 07 (Standard)  |  Cost Level 2</t>
+          <t>Item Roll Forward — Item 99955 / Branch BR1 / Location LOC1  |  Cost Method 07 (Standard)  |  Cost Level 2</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="B3" s="151" t="inlineStr">
         <is>
-          <t>1000000.141000.CC</t>
+          <t>9100000.611000.A1</t>
         </is>
       </c>
       <c r="C3" s="152" t="n">
@@ -1997,17 +1997,17 @@
       </c>
       <c r="D3" s="151" t="inlineStr">
         <is>
-          <t>IDM</t>
+          <t>BR1</t>
         </is>
       </c>
       <c r="E3" s="151" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>99955</t>
         </is>
       </c>
       <c r="F3" s="151" t="inlineStr">
         <is>
-          <t>MLD</t>
+          <t>LOC1</t>
         </is>
       </c>
       <c r="G3" s="151" t="n"/>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="B4" s="158" t="inlineStr">
         <is>
-          <t>1000000.141000.CC</t>
+          <t>9100000.611000.A1</t>
         </is>
       </c>
       <c r="C4" s="159" t="n">
@@ -2076,17 +2076,17 @@
       </c>
       <c r="D4" s="158" t="inlineStr">
         <is>
-          <t>IDM</t>
+          <t>BR1</t>
         </is>
       </c>
       <c r="E4" s="158" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>99955</t>
         </is>
       </c>
       <c r="F4" s="158" t="inlineStr">
         <is>
-          <t>MLD</t>
+          <t>LOC1</t>
         </is>
       </c>
       <c r="G4" s="158" t="n"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="K4" s="158" t="inlineStr">
         <is>
-          <t>WHS A MLD</t>
+          <t>WHS A LOC1</t>
         </is>
       </c>
       <c r="L4" s="161" t="n">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="B5" s="158" t="inlineStr">
         <is>
-          <t>1000000.141000.CC</t>
+          <t>9100000.611000.A1</t>
         </is>
       </c>
       <c r="C5" s="159" t="n">
@@ -2157,17 +2157,17 @@
       </c>
       <c r="D5" s="158" t="inlineStr">
         <is>
-          <t>IDM</t>
+          <t>BR1</t>
         </is>
       </c>
       <c r="E5" s="158" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>99955</t>
         </is>
       </c>
       <c r="F5" s="158" t="inlineStr">
         <is>
-          <t>MLD</t>
+          <t>LOC1</t>
         </is>
       </c>
       <c r="G5" s="158" t="n"/>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="B6" s="158" t="inlineStr">
         <is>
-          <t>1000000.141000.CC</t>
+          <t>9100000.611000.A1</t>
         </is>
       </c>
       <c r="C6" s="159" t="n">
@@ -2238,17 +2238,17 @@
       </c>
       <c r="D6" s="158" t="inlineStr">
         <is>
-          <t>IDM</t>
+          <t>BR1</t>
         </is>
       </c>
       <c r="E6" s="158" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>99955</t>
         </is>
       </c>
       <c r="F6" s="158" t="inlineStr">
         <is>
-          <t>MLD</t>
+          <t>LOC1</t>
         </is>
       </c>
       <c r="G6" s="158" t="n"/>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B7" s="158" t="inlineStr">
         <is>
-          <t>1000000.141000.CC</t>
+          <t>9100000.611000.A1</t>
         </is>
       </c>
       <c r="C7" s="159" t="n">
@@ -2319,17 +2319,17 @@
       </c>
       <c r="D7" s="158" t="inlineStr">
         <is>
-          <t>IDM</t>
+          <t>BR1</t>
         </is>
       </c>
       <c r="E7" s="158" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>99955</t>
         </is>
       </c>
       <c r="F7" s="158" t="inlineStr">
         <is>
-          <t>MLD</t>
+          <t>LOC1</t>
         </is>
       </c>
       <c r="G7" s="158" t="n"/>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="B8" s="158" t="inlineStr">
         <is>
-          <t>1000000.141000.CC</t>
+          <t>9100000.611000.A1</t>
         </is>
       </c>
       <c r="C8" s="159" t="n">
@@ -2400,17 +2400,17 @@
       </c>
       <c r="D8" s="158" t="inlineStr">
         <is>
-          <t>IDM</t>
+          <t>BR1</t>
         </is>
       </c>
       <c r="E8" s="158" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>99955</t>
         </is>
       </c>
       <c r="F8" s="158" t="inlineStr">
         <is>
-          <t>MLD</t>
+          <t>LOC1</t>
         </is>
       </c>
       <c r="G8" s="158" t="n"/>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="B9" s="158" t="inlineStr">
         <is>
-          <t>1000000.141000.CC</t>
+          <t>9100000.611000.A1</t>
         </is>
       </c>
       <c r="C9" s="159" t="n">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="D9" s="158" t="inlineStr">
         <is>
-          <t>IDM</t>
+          <t>BR1</t>
         </is>
       </c>
       <c r="E9" s="158" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>99955</t>
         </is>
       </c>
       <c r="F9" s="158" t="inlineStr">
         <is>
-          <t>MLD</t>
+          <t>LOC1</t>
         </is>
       </c>
       <c r="G9" s="158" t="n"/>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="B10" s="158" t="inlineStr">
         <is>
-          <t>1000000.141000.CC</t>
+          <t>9100000.611000.A1</t>
         </is>
       </c>
       <c r="C10" s="159" t="n">
@@ -2562,17 +2562,17 @@
       </c>
       <c r="D10" s="158" t="inlineStr">
         <is>
-          <t>IDM</t>
+          <t>BR1</t>
         </is>
       </c>
       <c r="E10" s="158" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>99955</t>
         </is>
       </c>
       <c r="F10" s="158" t="inlineStr">
         <is>
-          <t>MLD</t>
+          <t>LOC1</t>
         </is>
       </c>
       <c r="G10" s="158" t="n"/>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="B11" s="158" t="inlineStr">
         <is>
-          <t>1000000.141000.CC</t>
+          <t>9100000.611000.A1</t>
         </is>
       </c>
       <c r="C11" s="159" t="n">
@@ -2643,17 +2643,17 @@
       </c>
       <c r="D11" s="158" t="inlineStr">
         <is>
-          <t>IDM</t>
+          <t>BR1</t>
         </is>
       </c>
       <c r="E11" s="158" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>99955</t>
         </is>
       </c>
       <c r="F11" s="158" t="inlineStr">
         <is>
-          <t>MLD</t>
+          <t>LOC1</t>
         </is>
       </c>
       <c r="G11" s="158" t="n"/>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B12" s="158" t="inlineStr">
         <is>
-          <t>1000000.141000.CC</t>
+          <t>9100000.611000.A1</t>
         </is>
       </c>
       <c r="C12" s="159" t="n">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="D12" s="158" t="inlineStr">
         <is>
-          <t>IDM</t>
+          <t>BR1</t>
         </is>
       </c>
       <c r="E12" s="158" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>99955</t>
         </is>
       </c>
       <c r="F12" s="158" t="inlineStr">
         <is>
-          <t>MLD</t>
+          <t>LOC1</t>
         </is>
       </c>
       <c r="G12" s="158" t="n"/>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="B13" s="158" t="inlineStr">
         <is>
-          <t>1000000.141000.CC</t>
+          <t>9100000.611000.A1</t>
         </is>
       </c>
       <c r="C13" s="159" t="n">
@@ -2805,17 +2805,17 @@
       </c>
       <c r="D13" s="158" t="inlineStr">
         <is>
-          <t>IDM</t>
+          <t>BR1</t>
         </is>
       </c>
       <c r="E13" s="158" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>99955</t>
         </is>
       </c>
       <c r="F13" s="158" t="inlineStr">
         <is>
-          <t>MLD</t>
+          <t>LOC1</t>
         </is>
       </c>
       <c r="G13" s="158" t="n"/>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="B14" s="158" t="inlineStr">
         <is>
-          <t>1000000.141000.CC</t>
+          <t>9100000.611000.A1</t>
         </is>
       </c>
       <c r="C14" s="159" t="n">
@@ -2886,17 +2886,17 @@
       </c>
       <c r="D14" s="158" t="inlineStr">
         <is>
-          <t>IDM</t>
+          <t>BR1</t>
         </is>
       </c>
       <c r="E14" s="158" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>99955</t>
         </is>
       </c>
       <c r="F14" s="158" t="inlineStr">
         <is>
-          <t>MLD</t>
+          <t>LOC1</t>
         </is>
       </c>
       <c r="G14" s="158" t="n"/>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B15" s="158" t="inlineStr">
         <is>
-          <t>1000000.141000.CC</t>
+          <t>9100000.611000.A1</t>
         </is>
       </c>
       <c r="C15" s="159" t="n">
@@ -2967,17 +2967,17 @@
       </c>
       <c r="D15" s="158" t="inlineStr">
         <is>
-          <t>IDM</t>
+          <t>BR1</t>
         </is>
       </c>
       <c r="E15" s="158" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>99955</t>
         </is>
       </c>
       <c r="F15" s="158" t="inlineStr">
         <is>
-          <t>MLD</t>
+          <t>LOC1</t>
         </is>
       </c>
       <c r="G15" s="158" t="n"/>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="B16" s="158" t="inlineStr">
         <is>
-          <t>1000000.141000.CC</t>
+          <t>9100000.611000.A1</t>
         </is>
       </c>
       <c r="C16" s="159" t="n">
@@ -3048,17 +3048,17 @@
       </c>
       <c r="D16" s="158" t="inlineStr">
         <is>
-          <t>IDM</t>
+          <t>BR1</t>
         </is>
       </c>
       <c r="E16" s="158" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>99955</t>
         </is>
       </c>
       <c r="F16" s="158" t="inlineStr">
         <is>
-          <t>MLD</t>
+          <t>LOC1</t>
         </is>
       </c>
       <c r="G16" s="158" t="n"/>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="B17" s="158" t="inlineStr">
         <is>
-          <t>1000000.141000.CC</t>
+          <t>9100000.611000.A1</t>
         </is>
       </c>
       <c r="C17" s="159" t="n">
@@ -3129,17 +3129,17 @@
       </c>
       <c r="D17" s="158" t="inlineStr">
         <is>
-          <t>IDM</t>
+          <t>BR1</t>
         </is>
       </c>
       <c r="E17" s="158" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>99955</t>
         </is>
       </c>
       <c r="F17" s="158" t="inlineStr">
         <is>
-          <t>MLD</t>
+          <t>LOC1</t>
         </is>
       </c>
       <c r="G17" s="158" t="n"/>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="B18" s="158" t="inlineStr">
         <is>
-          <t>1000000.141000.CC</t>
+          <t>9100000.611000.A1</t>
         </is>
       </c>
       <c r="C18" s="159" t="n">
@@ -3210,17 +3210,17 @@
       </c>
       <c r="D18" s="158" t="inlineStr">
         <is>
-          <t>IDM</t>
+          <t>BR1</t>
         </is>
       </c>
       <c r="E18" s="158" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>99955</t>
         </is>
       </c>
       <c r="F18" s="158" t="inlineStr">
         <is>
-          <t>MLD</t>
+          <t>LOC1</t>
         </is>
       </c>
       <c r="G18" s="158" t="n"/>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="K18" s="158" t="inlineStr">
         <is>
-          <t>WHS A MLD</t>
+          <t>WHS A LOC1</t>
         </is>
       </c>
       <c r="L18" s="161" t="n">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="B19" s="158" t="inlineStr">
         <is>
-          <t>1000000.141000.CC</t>
+          <t>9100000.611000.A1</t>
         </is>
       </c>
       <c r="C19" s="159" t="n">
@@ -3291,17 +3291,17 @@
       </c>
       <c r="D19" s="158" t="inlineStr">
         <is>
-          <t>IDM</t>
+          <t>BR1</t>
         </is>
       </c>
       <c r="E19" s="158" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>99955</t>
         </is>
       </c>
       <c r="F19" s="158" t="inlineStr">
         <is>
-          <t>MLD</t>
+          <t>LOC1</t>
         </is>
       </c>
       <c r="G19" s="158" t="n"/>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="B20" s="158" t="inlineStr">
         <is>
-          <t>1000000.141000.CC</t>
+          <t>9100000.611000.A1</t>
         </is>
       </c>
       <c r="C20" s="159" t="n">
@@ -3372,17 +3372,17 @@
       </c>
       <c r="D20" s="158" t="inlineStr">
         <is>
-          <t>IDM</t>
+          <t>BR1</t>
         </is>
       </c>
       <c r="E20" s="158" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>99955</t>
         </is>
       </c>
       <c r="F20" s="158" t="inlineStr">
         <is>
-          <t>MLD</t>
+          <t>LOC1</t>
         </is>
       </c>
       <c r="G20" s="158" t="n"/>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="B21" s="165" t="inlineStr">
         <is>
-          <t>1000000.141000.CC</t>
+          <t>9100000.611000.A1</t>
         </is>
       </c>
       <c r="C21" s="166" t="n">
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D21" s="165" t="inlineStr">
         <is>
-          <t>IDM</t>
+          <t>BR1</t>
         </is>
       </c>
       <c r="E21" s="165" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>99955</t>
         </is>
       </c>
       <c r="F21" s="165" t="inlineStr">
         <is>
-          <t>MLD</t>
+          <t>LOC1</t>
         </is>
       </c>
       <c r="G21" s="165" t="n"/>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="B22" s="172" t="inlineStr">
         <is>
-          <t>1000000.141000.CC</t>
+          <t>9100000.611000.A1</t>
         </is>
       </c>
       <c r="C22" s="173" t="n">
@@ -3534,17 +3534,17 @@
       </c>
       <c r="D22" s="172" t="inlineStr">
         <is>
-          <t>IDM</t>
+          <t>BR1</t>
         </is>
       </c>
       <c r="E22" s="172" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>99955</t>
         </is>
       </c>
       <c r="F22" s="172" t="inlineStr">
         <is>
-          <t>MLD</t>
+          <t>LOC1</t>
         </is>
       </c>
       <c r="G22" s="172" t="n"/>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="B23" s="165" t="inlineStr">
         <is>
-          <t>1000000.141000.CC</t>
+          <t>9100000.611000.A1</t>
         </is>
       </c>
       <c r="C23" s="166" t="n">
@@ -3615,17 +3615,17 @@
       </c>
       <c r="D23" s="165" t="inlineStr">
         <is>
-          <t>IDM</t>
+          <t>BR1</t>
         </is>
       </c>
       <c r="E23" s="165" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>99955</t>
         </is>
       </c>
       <c r="F23" s="165" t="inlineStr">
         <is>
-          <t>MLD</t>
+          <t>LOC1</t>
         </is>
       </c>
       <c r="G23" s="165" t="n"/>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="B24" s="165" t="inlineStr">
         <is>
-          <t>1000000.141000.CC</t>
+          <t>9100000.611000.A1</t>
         </is>
       </c>
       <c r="C24" s="166" t="n">
@@ -3696,17 +3696,17 @@
       </c>
       <c r="D24" s="165" t="inlineStr">
         <is>
-          <t>IDM</t>
+          <t>BR1</t>
         </is>
       </c>
       <c r="E24" s="165" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>99955</t>
         </is>
       </c>
       <c r="F24" s="165" t="inlineStr">
         <is>
-          <t>MLD</t>
+          <t>LOC1</t>
         </is>
       </c>
       <c r="G24" s="165" t="n"/>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="B25" s="179" t="inlineStr">
         <is>
-          <t>1000000.141000.CC</t>
+          <t>9100000.611000.A1</t>
         </is>
       </c>
       <c r="C25" s="180" t="n">
@@ -3777,17 +3777,17 @@
       </c>
       <c r="D25" s="179" t="inlineStr">
         <is>
-          <t>IDM</t>
+          <t>BR1</t>
         </is>
       </c>
       <c r="E25" s="179" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>99955</t>
         </is>
       </c>
       <c r="F25" s="179" t="inlineStr">
         <is>
-          <t>MLD</t>
+          <t>LOC1</t>
         </is>
       </c>
       <c r="G25" s="179" t="n"/>
